--- a/data/titre.xlsx
+++ b/data/titre.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\My Drive\paper\Review\Protein\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pengb\PycharmProjects\protein_review\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AC7775A-81F5-4CCC-8AAD-C9BF59F129B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E18DDDC-F902-4DE6-B016-FC84C6A004DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="titre" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$M$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$M$61</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="689" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="165">
   <si>
     <t>Candida boidinii</t>
   </si>
@@ -561,6 +561,15 @@
   </si>
   <si>
     <t>https://www.sciencedirect.com/science/article/pii/S1359511325001813#fig0020</t>
+  </si>
+  <si>
+    <t>Collegan</t>
+  </si>
+  <si>
+    <t>https://bioresourcesbioprocessing.springeropen.com/articles/10.1186/s40643-022-00605-4#Sec18</t>
+  </si>
+  <si>
+    <t>https://bioresourcesbioprocessing.springeropen.com/articles/10.1186/s40643-022-00606-3</t>
   </si>
 </sst>
 </file>
@@ -952,7 +961,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M80"/>
+  <dimension ref="A1:M82"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.88671875" customWidth="1"/>
@@ -1797,7 +1806,7 @@
         <v>81</v>
       </c>
       <c r="K22">
-        <f t="shared" ref="K22:K36" si="3">I22/J22</f>
+        <f t="shared" ref="K22:K38" si="3">I22/J22</f>
         <v>5.5555555555555556E-4</v>
       </c>
       <c r="M22" s="1" t="s">
@@ -2207,7 +2216,7 @@
         <v>0.95833333333333337</v>
       </c>
       <c r="D33">
-        <f t="shared" ref="D33:D43" si="4">SUM(B33:C33)</f>
+        <f t="shared" ref="D33:D45" si="4">SUM(B33:C33)</f>
         <v>2024.9583333333333</v>
       </c>
       <c r="E33" t="s">
@@ -2349,12 +2358,12 @@
         <v>161</v>
       </c>
     </row>
-    <row r="37" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="10" t="s">
-        <v>157</v>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A37" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="B37">
-        <v>2010</v>
+        <v>2022</v>
       </c>
       <c r="C37">
         <f>10.5/12</f>
@@ -2362,67 +2371,69 @@
       </c>
       <c r="D37">
         <f t="shared" si="4"/>
-        <v>2010.875</v>
+        <v>2022.875</v>
       </c>
       <c r="E37" t="s">
-        <v>39</v>
+        <v>162</v>
       </c>
       <c r="F37" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
       <c r="H37" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="I37">
-        <v>5.0999999999999996</v>
+        <v>1.05</v>
       </c>
       <c r="J37">
-        <v>24.6</v>
+        <f>270*0.25</f>
+        <v>67.5</v>
       </c>
       <c r="K37">
-        <f t="shared" ref="K37:K40" si="5">I37/J37</f>
-        <v>0.20731707317073167</v>
+        <f t="shared" si="3"/>
+        <v>1.5555555555555557E-2</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="10" t="s">
-        <v>157</v>
+        <v>163</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A38" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="B38">
-        <v>2007</v>
+        <v>2022</v>
       </c>
       <c r="C38">
-        <f>6.5/12</f>
-        <v>0.54166666666666663</v>
+        <f>10.5/12</f>
+        <v>0.875</v>
       </c>
       <c r="D38">
-        <f t="shared" si="4"/>
-        <v>2007.5416666666667</v>
+        <f t="shared" ref="D38" si="5">SUM(B38:C38)</f>
+        <v>2022.875</v>
       </c>
       <c r="E38" t="s">
-        <v>39</v>
+        <v>162</v>
       </c>
       <c r="F38" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
       <c r="H38" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="I38">
-        <v>0.38500000000000001</v>
+        <v>2.33</v>
       </c>
       <c r="J38">
-        <v>60</v>
+        <f>405*0.25</f>
+        <v>101.25</v>
       </c>
       <c r="K38">
-        <f t="shared" si="5"/>
-        <v>6.4166666666666669E-3</v>
+        <f t="shared" si="3"/>
+        <v>2.3012345679012346E-2</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>124</v>
+        <v>164</v>
       </c>
     </row>
     <row r="39" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -2430,37 +2441,37 @@
         <v>157</v>
       </c>
       <c r="B39">
-        <v>1999</v>
+        <v>2010</v>
       </c>
       <c r="C39">
-        <f>4.5/12</f>
-        <v>0.375</v>
+        <f>10.5/12</f>
+        <v>0.875</v>
       </c>
       <c r="D39">
         <f t="shared" si="4"/>
-        <v>1999.375</v>
+        <v>2010.875</v>
       </c>
       <c r="E39" t="s">
-        <v>126</v>
+        <v>39</v>
       </c>
       <c r="F39" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="H39" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="I39">
-        <v>13.49</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="J39">
-        <v>125</v>
+        <v>24.6</v>
       </c>
       <c r="K39">
-        <f t="shared" si="5"/>
-        <v>0.10792</v>
+        <f t="shared" ref="K39:K42" si="6">I39/J39</f>
+        <v>0.20731707317073167</v>
       </c>
       <c r="M39" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -2468,37 +2479,37 @@
         <v>157</v>
       </c>
       <c r="B40">
-        <v>2012</v>
+        <v>2007</v>
       </c>
       <c r="C40">
-        <f>11.5/12</f>
-        <v>0.95833333333333337</v>
+        <f>6.5/12</f>
+        <v>0.54166666666666663</v>
       </c>
       <c r="D40">
         <f t="shared" si="4"/>
-        <v>2012.9583333333333</v>
+        <v>2007.5416666666667</v>
       </c>
       <c r="E40" t="s">
-        <v>127</v>
+        <v>39</v>
       </c>
       <c r="F40" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="H40" t="s">
         <v>31</v>
       </c>
       <c r="I40">
-        <v>1.109</v>
+        <v>0.38500000000000001</v>
       </c>
       <c r="J40">
-        <v>127.8</v>
+        <v>60</v>
       </c>
       <c r="K40">
-        <f t="shared" si="5"/>
-        <v>8.677621283255086E-3</v>
+        <f t="shared" si="6"/>
+        <v>6.4166666666666669E-3</v>
       </c>
       <c r="M40" s="1" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -2506,7 +2517,7 @@
         <v>157</v>
       </c>
       <c r="B41">
-        <v>2016</v>
+        <v>1999</v>
       </c>
       <c r="C41">
         <f>4.5/12</f>
@@ -2514,100 +2525,99 @@
       </c>
       <c r="D41">
         <f t="shared" si="4"/>
+        <v>1999.375</v>
+      </c>
+      <c r="E41" t="s">
+        <v>126</v>
+      </c>
+      <c r="F41" t="s">
+        <v>126</v>
+      </c>
+      <c r="H41" t="s">
+        <v>10</v>
+      </c>
+      <c r="I41">
+        <v>13.49</v>
+      </c>
+      <c r="J41">
+        <v>125</v>
+      </c>
+      <c r="K41">
+        <f t="shared" si="6"/>
+        <v>0.10792</v>
+      </c>
+      <c r="M41" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A42" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="B42">
+        <v>2012</v>
+      </c>
+      <c r="C42">
+        <f>11.5/12</f>
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="D42">
+        <f t="shared" si="4"/>
+        <v>2012.9583333333333</v>
+      </c>
+      <c r="E42" t="s">
+        <v>127</v>
+      </c>
+      <c r="F42" t="s">
+        <v>127</v>
+      </c>
+      <c r="H42" t="s">
+        <v>31</v>
+      </c>
+      <c r="I42">
+        <v>1.109</v>
+      </c>
+      <c r="J42">
+        <v>127.8</v>
+      </c>
+      <c r="K42">
+        <f t="shared" si="6"/>
+        <v>8.677621283255086E-3</v>
+      </c>
+      <c r="M42" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A43" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="B43">
+        <v>2016</v>
+      </c>
+      <c r="C43">
+        <f>4.5/12</f>
+        <v>0.375</v>
+      </c>
+      <c r="D43">
+        <f t="shared" si="4"/>
         <v>2016.375</v>
       </c>
-      <c r="E41" t="s">
+      <c r="E43" t="s">
         <v>129</v>
       </c>
-      <c r="F41" t="s">
+      <c r="F43" t="s">
         <v>129</v>
       </c>
-      <c r="H41" t="s">
-        <v>10</v>
-      </c>
-      <c r="K41">
+      <c r="H43" t="s">
+        <v>10</v>
+      </c>
+      <c r="K43">
         <f>244.5*52000/1000000000</f>
         <v>1.2714E-2</v>
       </c>
-      <c r="M41" s="1" t="s">
+      <c r="M43" s="1" t="s">
         <v>130</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>0</v>
-      </c>
-      <c r="B42">
-        <v>1996</v>
-      </c>
-      <c r="C42">
-        <f>6.5/12</f>
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="D42">
-        <f t="shared" si="4"/>
-        <v>1996.5416666666667</v>
-      </c>
-      <c r="E42" t="s">
-        <v>6</v>
-      </c>
-      <c r="F42" t="s">
-        <v>88</v>
-      </c>
-      <c r="H42" t="s">
-        <v>10</v>
-      </c>
-      <c r="I42">
-        <v>3.5</v>
-      </c>
-      <c r="J42">
-        <v>90</v>
-      </c>
-      <c r="K42">
-        <f>I42/J42</f>
-        <v>3.888888888888889E-2</v>
-      </c>
-      <c r="M42" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>0</v>
-      </c>
-      <c r="B43">
-        <v>2002</v>
-      </c>
-      <c r="C43">
-        <f>5.5/12</f>
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D43">
-        <f t="shared" si="4"/>
-        <v>2002.4583333333333</v>
-      </c>
-      <c r="E43" t="s">
-        <v>97</v>
-      </c>
-      <c r="F43" t="s">
-        <v>148</v>
-      </c>
-      <c r="H43" t="s">
-        <v>10</v>
-      </c>
-      <c r="I43">
-        <v>1.2E-2</v>
-      </c>
-      <c r="J43">
-        <f>150*0.25</f>
-        <v>37.5</v>
-      </c>
-      <c r="K43">
-        <f>I43/J43</f>
-        <v>3.2000000000000003E-4</v>
-      </c>
-      <c r="M43" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
@@ -2615,113 +2625,114 @@
         <v>0</v>
       </c>
       <c r="B44">
-        <v>2004</v>
+        <v>1996</v>
       </c>
       <c r="C44">
         <f>6.5/12</f>
         <v>0.54166666666666663</v>
       </c>
       <c r="D44">
-        <f t="shared" ref="D44" si="6">SUM(B44:C44)</f>
-        <v>2004.5416666666667</v>
+        <f t="shared" si="4"/>
+        <v>1996.5416666666667</v>
       </c>
       <c r="E44" t="s">
-        <v>99</v>
+        <v>6</v>
       </c>
       <c r="F44" t="s">
-        <v>149</v>
+        <v>88</v>
       </c>
       <c r="H44" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="I44">
-        <v>8.6999999999999994E-2</v>
+        <v>3.5</v>
       </c>
       <c r="J44">
-        <v>24</v>
+        <v>90</v>
       </c>
       <c r="K44">
         <f>I44/J44</f>
-        <v>3.6249999999999998E-3</v>
+        <v>3.888888888888889E-2</v>
       </c>
       <c r="M44" s="1" t="s">
-        <v>121</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="B45">
-        <v>2022</v>
+        <v>2002</v>
       </c>
       <c r="C45">
-        <f>2.5/12</f>
-        <v>0.20833333333333334</v>
+        <f>5.5/12</f>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D45">
-        <f>SUM(B45:C45)</f>
-        <v>2022.2083333333333</v>
-      </c>
-      <c r="E45" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F45" s="4" t="s">
-        <v>36</v>
+        <f t="shared" si="4"/>
+        <v>2002.4583333333333</v>
+      </c>
+      <c r="E45" t="s">
+        <v>97</v>
+      </c>
+      <c r="F45" t="s">
+        <v>148</v>
       </c>
       <c r="H45" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="I45">
-        <v>0.53</v>
+        <v>1.2E-2</v>
       </c>
       <c r="J45">
-        <v>100</v>
+        <f>150*0.25</f>
+        <v>37.5</v>
       </c>
       <c r="K45">
         <f>I45/J45</f>
-        <v>5.3E-3</v>
-      </c>
-      <c r="M45" s="1" t="s">
-        <v>37</v>
+        <v>3.2000000000000003E-4</v>
+      </c>
+      <c r="M45" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="B46">
-        <v>2018</v>
+        <v>2004</v>
       </c>
       <c r="C46">
-        <f>10.5/12</f>
-        <v>0.875</v>
+        <f>6.5/12</f>
+        <v>0.54166666666666663</v>
       </c>
       <c r="D46">
-        <f>SUM(B46:C46)</f>
-        <v>2018.875</v>
+        <f t="shared" ref="D46" si="7">SUM(B46:C46)</f>
+        <v>2004.5416666666667</v>
       </c>
       <c r="E46" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="F46" t="s">
-        <v>88</v>
+        <v>149</v>
       </c>
       <c r="H46" t="s">
         <v>31</v>
       </c>
-      <c r="I46" s="6">
-        <v>2.5</v>
-      </c>
-      <c r="J46" s="6">
-        <v>98.5</v>
+      <c r="I46">
+        <v>8.6999999999999994E-2</v>
+      </c>
+      <c r="J46">
+        <v>24</v>
       </c>
       <c r="K46">
         <f>I46/J46</f>
-        <v>2.5380710659898477E-2</v>
-      </c>
-      <c r="M46" t="s">
-        <v>89</v>
+        <v>3.6249999999999998E-3</v>
+      </c>
+      <c r="M46" s="1" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.3">
@@ -2729,31 +2740,37 @@
         <v>35</v>
       </c>
       <c r="B47">
-        <v>2000</v>
+        <v>2022</v>
       </c>
       <c r="C47">
-        <f>1.5/12</f>
-        <v>0.125</v>
+        <f>2.5/12</f>
+        <v>0.20833333333333334</v>
       </c>
       <c r="D47">
         <f>SUM(B47:C47)</f>
-        <v>2000.125</v>
-      </c>
-      <c r="E47" t="s">
-        <v>12</v>
-      </c>
-      <c r="F47" t="s">
-        <v>12</v>
+        <v>2022.2083333333333</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="H47" t="s">
         <v>31</v>
       </c>
+      <c r="I47">
+        <v>0.53</v>
+      </c>
+      <c r="J47">
+        <v>100</v>
+      </c>
       <c r="K47">
-        <f>0.0093/0.4</f>
-        <v>2.3249999999999996E-2</v>
+        <f>I47/J47</f>
+        <v>5.3E-3</v>
       </c>
       <c r="M47" s="1" t="s">
-        <v>90</v>
+        <v>37</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.3">
@@ -2761,15 +2778,15 @@
         <v>35</v>
       </c>
       <c r="B48">
-        <v>2013</v>
+        <v>2018</v>
       </c>
       <c r="C48">
-        <f>11.5/12</f>
-        <v>0.95833333333333337</v>
+        <f>10.5/12</f>
+        <v>0.875</v>
       </c>
       <c r="D48">
-        <f t="shared" ref="D48:D51" si="7">SUM(B48:C48)</f>
-        <v>2013.9583333333333</v>
+        <f>SUM(B48:C48)</f>
+        <v>2018.875</v>
       </c>
       <c r="E48" t="s">
         <v>88</v>
@@ -2780,11 +2797,18 @@
       <c r="H48" t="s">
         <v>31</v>
       </c>
+      <c r="I48" s="6">
+        <v>2.5</v>
+      </c>
+      <c r="J48" s="6">
+        <v>98.5</v>
+      </c>
       <c r="K48">
-        <v>1.4E-2</v>
+        <f>I48/J48</f>
+        <v>2.5380710659898477E-2</v>
       </c>
       <c r="M48" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.3">
@@ -2792,30 +2816,31 @@
         <v>35</v>
       </c>
       <c r="B49">
-        <v>2012</v>
+        <v>2000</v>
       </c>
       <c r="C49">
-        <f>11.5/12</f>
-        <v>0.95833333333333337</v>
+        <f>1.5/12</f>
+        <v>0.125</v>
       </c>
       <c r="D49">
-        <f t="shared" si="7"/>
-        <v>2012.9583333333333</v>
-      </c>
-      <c r="E49" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="F49" s="4" t="s">
-        <v>150</v>
+        <f>SUM(B49:C49)</f>
+        <v>2000.125</v>
+      </c>
+      <c r="E49" t="s">
+        <v>12</v>
+      </c>
+      <c r="F49" t="s">
+        <v>12</v>
       </c>
       <c r="H49" t="s">
         <v>31</v>
       </c>
       <c r="K49">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="M49" t="s">
-        <v>91</v>
+        <f>0.0093/0.4</f>
+        <v>2.3249999999999996E-2</v>
+      </c>
+      <c r="M49" s="1" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.3">
@@ -2823,37 +2848,30 @@
         <v>35</v>
       </c>
       <c r="B50">
-        <v>2024</v>
+        <v>2013</v>
       </c>
       <c r="C50">
-        <f>7.5/12</f>
-        <v>0.625</v>
+        <f>11.5/12</f>
+        <v>0.95833333333333337</v>
       </c>
       <c r="D50">
-        <f t="shared" si="7"/>
-        <v>2024.625</v>
-      </c>
-      <c r="E50" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="F50" s="7" t="s">
-        <v>93</v>
+        <f t="shared" ref="D50:D53" si="8">SUM(B50:C50)</f>
+        <v>2013.9583333333333</v>
+      </c>
+      <c r="E50" t="s">
+        <v>88</v>
+      </c>
+      <c r="F50" t="s">
+        <v>88</v>
       </c>
       <c r="H50" t="s">
         <v>31</v>
       </c>
-      <c r="I50">
-        <v>0.11600000000000001</v>
-      </c>
-      <c r="J50">
-        <f>225*0.23</f>
-        <v>51.75</v>
-      </c>
       <c r="K50">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="M50" s="1" t="s">
-        <v>94</v>
+        <v>1.4E-2</v>
+      </c>
+      <c r="M50" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.3">
@@ -2861,141 +2879,132 @@
         <v>35</v>
       </c>
       <c r="B51">
+        <v>2012</v>
+      </c>
+      <c r="C51">
+        <f>11.5/12</f>
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="D51">
+        <f t="shared" si="8"/>
+        <v>2012.9583333333333</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="H51" t="s">
+        <v>31</v>
+      </c>
+      <c r="K51">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="M51" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>35</v>
+      </c>
+      <c r="B52">
+        <v>2024</v>
+      </c>
+      <c r="C52">
+        <f>7.5/12</f>
+        <v>0.625</v>
+      </c>
+      <c r="D52">
+        <f t="shared" si="8"/>
+        <v>2024.625</v>
+      </c>
+      <c r="E52" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="F52" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="H52" t="s">
+        <v>31</v>
+      </c>
+      <c r="I52">
+        <v>0.11600000000000001</v>
+      </c>
+      <c r="J52">
+        <f>225*0.23</f>
+        <v>51.75</v>
+      </c>
+      <c r="K52">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="M52" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>35</v>
+      </c>
+      <c r="B53">
         <v>2016</v>
       </c>
-      <c r="C51">
+      <c r="C53">
         <f>5.5/12</f>
         <v>0.45833333333333331</v>
       </c>
-      <c r="D51">
-        <f t="shared" si="7"/>
+      <c r="D53">
+        <f t="shared" si="8"/>
         <v>2016.4583333333333</v>
       </c>
-      <c r="E51" t="s">
+      <c r="E53" t="s">
         <v>95</v>
       </c>
-      <c r="F51" t="s">
+      <c r="F53" t="s">
         <v>95</v>
       </c>
-      <c r="H51" t="s">
-        <v>31</v>
-      </c>
-      <c r="K51">
+      <c r="H53" t="s">
+        <v>31</v>
+      </c>
+      <c r="K53">
         <f>0.0002027/0.23</f>
         <v>8.8130434782608691E-4</v>
       </c>
-      <c r="M51" s="1" t="s">
+      <c r="M53" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
         <v>102</v>
       </c>
-      <c r="B52">
+      <c r="B54">
         <v>2022</v>
       </c>
-      <c r="C52">
+      <c r="C54">
         <f>6.5/12</f>
         <v>0.54166666666666663</v>
       </c>
-      <c r="D52">
-        <f t="shared" ref="D52" si="8">SUM(B52:C52)</f>
+      <c r="D54">
+        <f t="shared" ref="D54" si="9">SUM(B54:C54)</f>
         <v>2022.5416666666667</v>
       </c>
-      <c r="E52" s="8" t="s">
+      <c r="E54" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="F52" s="8" t="s">
+      <c r="F54" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="H52" t="s">
-        <v>31</v>
-      </c>
-      <c r="K52">
+      <c r="H54" t="s">
+        <v>31</v>
+      </c>
+      <c r="K54">
         <f>0.000349/0.35</f>
         <v>9.9714285714285725E-4</v>
       </c>
-      <c r="M52" s="1" t="s">
+      <c r="M54" s="1" t="s">
         <v>104</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
-        <v>105</v>
-      </c>
-      <c r="B53">
-        <v>2013</v>
-      </c>
-      <c r="C53">
-        <f>7.5/12</f>
-        <v>0.625</v>
-      </c>
-      <c r="D53">
-        <f t="shared" ref="D53:D59" si="9">SUM(B53:C53)</f>
-        <v>2013.625</v>
-      </c>
-      <c r="E53" t="s">
-        <v>106</v>
-      </c>
-      <c r="F53" t="s">
-        <v>106</v>
-      </c>
-      <c r="H53" t="s">
-        <v>31</v>
-      </c>
-      <c r="I53">
-        <v>0.104</v>
-      </c>
-      <c r="J53">
-        <f>40*0.51</f>
-        <v>20.399999999999999</v>
-      </c>
-      <c r="K53">
-        <f>I53/J53</f>
-        <v>5.0980392156862748E-3</v>
-      </c>
-      <c r="M53" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
-        <v>105</v>
-      </c>
-      <c r="B54">
-        <v>2014</v>
-      </c>
-      <c r="C54">
-        <f>11.5/12</f>
-        <v>0.95833333333333337</v>
-      </c>
-      <c r="D54">
-        <f t="shared" si="9"/>
-        <v>2014.9583333333333</v>
-      </c>
-      <c r="E54" t="s">
-        <v>112</v>
-      </c>
-      <c r="F54" t="s">
-        <v>134</v>
-      </c>
-      <c r="H54" t="s">
-        <v>31</v>
-      </c>
-      <c r="I54">
-        <v>0.23699999999999999</v>
-      </c>
-      <c r="J54">
-        <f>40*0.51</f>
-        <v>20.399999999999999</v>
-      </c>
-      <c r="K54">
-        <f t="shared" ref="K54:K59" si="10">I54/J54</f>
-        <v>1.1617647058823529E-2</v>
-      </c>
-      <c r="M54" s="1" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.3">
@@ -3003,38 +3012,38 @@
         <v>105</v>
       </c>
       <c r="B55">
-        <v>2004</v>
+        <v>2013</v>
       </c>
       <c r="C55">
-        <f>11.5/12</f>
-        <v>0.95833333333333337</v>
+        <f>7.5/12</f>
+        <v>0.625</v>
       </c>
       <c r="D55">
-        <f t="shared" si="9"/>
-        <v>2004.9583333333333</v>
+        <f t="shared" ref="D55:D61" si="10">SUM(B55:C55)</f>
+        <v>2013.625</v>
       </c>
       <c r="E55" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="F55" t="s">
-        <v>151</v>
+        <v>106</v>
       </c>
       <c r="H55" t="s">
         <v>31</v>
       </c>
       <c r="I55">
-        <v>0.1</v>
+        <v>0.104</v>
       </c>
       <c r="J55">
-        <f>20*0.51</f>
-        <v>10.199999999999999</v>
+        <f>40*0.51</f>
+        <v>20.399999999999999</v>
       </c>
       <c r="K55">
-        <f t="shared" si="10"/>
-        <v>9.8039215686274526E-3</v>
+        <f>I55/J55</f>
+        <v>5.0980392156862748E-3</v>
       </c>
       <c r="M55" s="1" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.3">
@@ -3042,255 +3051,295 @@
         <v>105</v>
       </c>
       <c r="B56">
+        <v>2014</v>
+      </c>
+      <c r="C56">
+        <f>11.5/12</f>
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="D56">
+        <f t="shared" si="10"/>
+        <v>2014.9583333333333</v>
+      </c>
+      <c r="E56" t="s">
+        <v>112</v>
+      </c>
+      <c r="F56" t="s">
+        <v>134</v>
+      </c>
+      <c r="H56" t="s">
+        <v>31</v>
+      </c>
+      <c r="I56">
+        <v>0.23699999999999999</v>
+      </c>
+      <c r="J56">
+        <f>40*0.51</f>
+        <v>20.399999999999999</v>
+      </c>
+      <c r="K56">
+        <f t="shared" ref="K56:K61" si="11">I56/J56</f>
+        <v>1.1617647058823529E-2</v>
+      </c>
+      <c r="M56" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>105</v>
+      </c>
+      <c r="B57">
+        <v>2004</v>
+      </c>
+      <c r="C57">
+        <f>11.5/12</f>
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="D57">
+        <f t="shared" si="10"/>
+        <v>2004.9583333333333</v>
+      </c>
+      <c r="E57" t="s">
+        <v>114</v>
+      </c>
+      <c r="F57" t="s">
+        <v>151</v>
+      </c>
+      <c r="H57" t="s">
+        <v>31</v>
+      </c>
+      <c r="I57">
+        <v>0.1</v>
+      </c>
+      <c r="J57">
+        <f>20*0.51</f>
+        <v>10.199999999999999</v>
+      </c>
+      <c r="K57">
+        <f t="shared" si="11"/>
+        <v>9.8039215686274526E-3</v>
+      </c>
+      <c r="M57" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>105</v>
+      </c>
+      <c r="B58">
         <v>1997</v>
       </c>
-      <c r="C56">
+      <c r="C58">
         <f>7.5/12</f>
         <v>0.625</v>
       </c>
-      <c r="D56">
-        <f t="shared" si="9"/>
+      <c r="D58">
+        <f t="shared" si="10"/>
         <v>1997.625</v>
       </c>
-      <c r="E56" t="s">
+      <c r="E58" t="s">
         <v>116</v>
       </c>
-      <c r="F56" t="s">
+      <c r="F58" t="s">
         <v>152</v>
       </c>
-      <c r="H56" t="s">
-        <v>31</v>
-      </c>
-      <c r="I56">
+      <c r="H58" t="s">
+        <v>31</v>
+      </c>
+      <c r="I58">
         <v>0.13</v>
       </c>
-      <c r="J56">
+      <c r="J58">
         <f>20*0.51</f>
         <v>10.199999999999999</v>
       </c>
-      <c r="K56">
-        <f t="shared" si="10"/>
+      <c r="K58">
+        <f t="shared" si="11"/>
         <v>1.2745098039215688E-2</v>
       </c>
-      <c r="M56" s="1" t="s">
+      <c r="M58" s="1" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
         <v>108</v>
       </c>
-      <c r="B57">
+      <c r="B59">
         <v>1991</v>
       </c>
-      <c r="C57">
+      <c r="C59">
         <f>9.5/12</f>
         <v>0.79166666666666663</v>
       </c>
-      <c r="D57">
-        <f t="shared" si="9"/>
+      <c r="D59">
+        <f t="shared" si="10"/>
         <v>1991.7916666666667</v>
       </c>
-      <c r="E57" t="s">
+      <c r="E59" t="s">
         <v>39</v>
       </c>
-      <c r="F57" t="s">
+      <c r="F59" t="s">
         <v>140</v>
       </c>
-      <c r="H57" t="s">
-        <v>31</v>
-      </c>
-      <c r="I57">
+      <c r="H59" t="s">
+        <v>31</v>
+      </c>
+      <c r="I59">
         <v>0.29599999999999999</v>
       </c>
-      <c r="J57">
+      <c r="J59">
         <v>8</v>
       </c>
-      <c r="K57">
-        <f t="shared" si="10"/>
+      <c r="K59">
+        <f t="shared" si="11"/>
         <v>3.6999999999999998E-2</v>
       </c>
-      <c r="M57" s="1" t="s">
+      <c r="M59" s="1" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
         <v>108</v>
       </c>
-      <c r="B58">
+      <c r="B60">
         <v>1994</v>
       </c>
-      <c r="C58">
+      <c r="C60">
         <f>9.5/12</f>
         <v>0.79166666666666663</v>
       </c>
-      <c r="D58">
-        <f t="shared" si="9"/>
+      <c r="D60">
+        <f t="shared" si="10"/>
         <v>1994.7916666666667</v>
       </c>
-      <c r="E58" t="s">
+      <c r="E60" t="s">
         <v>39</v>
       </c>
-      <c r="F58" t="s">
+      <c r="F60" t="s">
         <v>140</v>
       </c>
-      <c r="H58" t="s">
-        <v>10</v>
-      </c>
-      <c r="I58">
+      <c r="H60" t="s">
+        <v>10</v>
+      </c>
+      <c r="I60">
         <v>6.2E-2</v>
       </c>
-      <c r="J58">
+      <c r="J60">
         <v>35</v>
       </c>
-      <c r="K58">
-        <f t="shared" si="10"/>
+      <c r="K60">
+        <f t="shared" si="11"/>
         <v>1.7714285714285714E-3</v>
       </c>
-      <c r="M58" s="1" t="s">
+      <c r="M60" s="1" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="59" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A59" s="10" t="s">
+    <row r="61" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A61" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="B59">
+      <c r="B61">
         <v>2025</v>
       </c>
-      <c r="C59">
+      <c r="C61">
         <f>11.5/12</f>
         <v>0.95833333333333337</v>
       </c>
-      <c r="D59">
-        <f t="shared" si="9"/>
+      <c r="D61">
+        <f t="shared" si="10"/>
         <v>2025.9583333333333</v>
       </c>
-      <c r="E59" t="s">
+      <c r="E61" t="s">
         <v>154</v>
       </c>
-      <c r="F59" t="s">
+      <c r="F61" t="s">
         <v>154</v>
       </c>
-      <c r="H59" t="s">
-        <v>31</v>
-      </c>
-      <c r="I59">
+      <c r="H61" t="s">
+        <v>31</v>
+      </c>
+      <c r="I61">
         <v>3.456</v>
       </c>
-      <c r="J59">
+      <c r="J61">
         <f>316.3*0.35</f>
         <v>110.705</v>
       </c>
-      <c r="K59">
-        <f t="shared" si="10"/>
+      <c r="K61">
+        <f t="shared" si="11"/>
         <v>3.1218102163407254E-2</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
         <v>131</v>
       </c>
-      <c r="M65" t="s">
+      <c r="M67" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
         <v>108</v>
       </c>
-      <c r="B73">
+      <c r="B75">
         <v>2024</v>
       </c>
-      <c r="C73">
+      <c r="C75">
         <f>2.5/12</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="D73">
-        <f>SUM(B73:C73)</f>
+      <c r="D75">
+        <f>SUM(B75:C75)</f>
         <v>2024.2083333333333</v>
       </c>
-      <c r="E73" t="s">
+      <c r="E75" t="s">
         <v>6</v>
       </c>
-      <c r="H73" t="s">
-        <v>10</v>
-      </c>
-      <c r="I73">
+      <c r="H75" t="s">
+        <v>10</v>
+      </c>
+      <c r="I75">
         <v>16.8</v>
       </c>
-      <c r="M73" s="1" t="s">
+      <c r="M75" s="1" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A74" s="9" t="s">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A76" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="I74">
+      <c r="I76">
         <v>0.08</v>
       </c>
-      <c r="M74" t="s">
+      <c r="M76" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="75" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A75" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B75">
+    <row r="77" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A77" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B77">
         <v>2023</v>
       </c>
-      <c r="E75" t="s">
+      <c r="E77" t="s">
         <v>12</v>
       </c>
-      <c r="H75" t="s">
-        <v>10</v>
-      </c>
-      <c r="I75">
+      <c r="H77" t="s">
+        <v>10</v>
+      </c>
+      <c r="I77">
         <v>3.7</v>
       </c>
-      <c r="M75" s="3" t="s">
+      <c r="M77" s="3" t="s">
         <v>63</v>
-      </c>
-    </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A76" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B76">
-        <v>2025</v>
-      </c>
-      <c r="E76" t="s">
-        <v>16</v>
-      </c>
-      <c r="L76" t="s">
-        <v>15</v>
-      </c>
-      <c r="M76" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A77" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B77">
-        <v>2015</v>
-      </c>
-      <c r="E77" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="F77" s="4"/>
-      <c r="H77" t="s">
-        <v>31</v>
-      </c>
-      <c r="I77">
-        <v>0.2</v>
-      </c>
-      <c r="M77" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.3">
@@ -3298,65 +3347,103 @@
         <v>11</v>
       </c>
       <c r="B78">
+        <v>2025</v>
+      </c>
+      <c r="E78" t="s">
+        <v>16</v>
+      </c>
+      <c r="L78" t="s">
+        <v>15</v>
+      </c>
+      <c r="M78" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A79" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B79">
+        <v>2015</v>
+      </c>
+      <c r="E79" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F79" s="4"/>
+      <c r="H79" t="s">
+        <v>31</v>
+      </c>
+      <c r="I79">
+        <v>0.2</v>
+      </c>
+      <c r="M79" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A80" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B80">
         <v>1997</v>
       </c>
-      <c r="E78" t="s">
+      <c r="E80" t="s">
         <v>66</v>
       </c>
-      <c r="H78" t="s">
-        <v>10</v>
-      </c>
-      <c r="I78">
+      <c r="H80" t="s">
+        <v>10</v>
+      </c>
+      <c r="I80">
         <v>0.2</v>
       </c>
-      <c r="M78" t="s">
+      <c r="M80" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A79" t="s">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
         <v>105</v>
       </c>
-      <c r="B79">
+      <c r="B81">
         <v>1991</v>
       </c>
-      <c r="C79">
+      <c r="C81">
         <f>7.5/12</f>
         <v>0.625</v>
       </c>
-      <c r="D79">
-        <f>SUM(B79:C79)</f>
+      <c r="D81">
+        <f>SUM(B81:C81)</f>
         <v>1991.625</v>
       </c>
-      <c r="E79" t="s">
+      <c r="E81" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A80" t="s">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
         <v>108</v>
       </c>
-      <c r="B80">
+      <c r="B82">
         <v>1993</v>
       </c>
-      <c r="C80">
+      <c r="C82">
         <f>10.5/12</f>
         <v>0.875</v>
       </c>
-      <c r="D80">
-        <f t="shared" ref="D80" si="11">SUM(B80:C80)</f>
+      <c r="D82">
+        <f t="shared" ref="D82" si="12">SUM(B82:C82)</f>
         <v>1993.875</v>
       </c>
-      <c r="E80" t="s">
+      <c r="E82" t="s">
         <v>109</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M59" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:M61" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <hyperlinks>
-    <hyperlink ref="M42" r:id="rId1" xr:uid="{2C6F6E23-ECE2-48FD-9281-2D99D7593433}"/>
-    <hyperlink ref="M75" r:id="rId2" location="Sec2234" xr:uid="{62C0EF63-5AB8-4BA9-8B91-BED051CAB1BF}"/>
-    <hyperlink ref="M76" r:id="rId3" xr:uid="{B20578A3-8323-4DE4-85AE-68D7FF9E102B}"/>
+    <hyperlink ref="M44" r:id="rId1" xr:uid="{2C6F6E23-ECE2-48FD-9281-2D99D7593433}"/>
+    <hyperlink ref="M77" r:id="rId2" location="Sec2234" xr:uid="{62C0EF63-5AB8-4BA9-8B91-BED051CAB1BF}"/>
+    <hyperlink ref="M78" r:id="rId3" xr:uid="{B20578A3-8323-4DE4-85AE-68D7FF9E102B}"/>
     <hyperlink ref="M2" r:id="rId4" location="Sec2" xr:uid="{E3E93F9E-DE58-4D08-B99F-BCC6036F7008}"/>
     <hyperlink ref="M3" r:id="rId5" xr:uid="{D9A4AF65-DA70-469D-830F-18C855356D90}"/>
     <hyperlink ref="M4" r:id="rId6" xr:uid="{B12BC68D-68E4-4106-B5E4-E526B322A8A6}"/>
@@ -3384,28 +3471,30 @@
     <hyperlink ref="M11" r:id="rId28" xr:uid="{F4B38A8C-4738-4863-988E-62EDE0DDB3C8}"/>
     <hyperlink ref="M8" r:id="rId29" xr:uid="{EB34F27E-0B05-4195-B7F0-D388A7AD2D27}"/>
     <hyperlink ref="M6" r:id="rId30" xr:uid="{15DB38CB-6521-44E4-B260-EDC4586943ED}"/>
-    <hyperlink ref="M45" r:id="rId31" location="Sec2" xr:uid="{235DA6CA-59BB-493F-AE3F-01F1CACCC335}"/>
-    <hyperlink ref="M47" r:id="rId32" location="BIB8" xr:uid="{93BE3110-5F69-4CA6-9551-CCF063F7F511}"/>
-    <hyperlink ref="M50" r:id="rId33" xr:uid="{1DFC047B-89FD-4940-B346-4D1719C84B8D}"/>
-    <hyperlink ref="M51" r:id="rId34" location="Sec11" xr:uid="{CF173C6B-1889-4F7C-B611-E21261B20B04}"/>
+    <hyperlink ref="M47" r:id="rId31" location="Sec2" xr:uid="{235DA6CA-59BB-493F-AE3F-01F1CACCC335}"/>
+    <hyperlink ref="M49" r:id="rId32" location="BIB8" xr:uid="{93BE3110-5F69-4CA6-9551-CCF063F7F511}"/>
+    <hyperlink ref="M52" r:id="rId33" xr:uid="{1DFC047B-89FD-4940-B346-4D1719C84B8D}"/>
+    <hyperlink ref="M53" r:id="rId34" location="Sec11" xr:uid="{CF173C6B-1889-4F7C-B611-E21261B20B04}"/>
     <hyperlink ref="M34" r:id="rId35" xr:uid="{1D1CA4DD-57EB-4FDA-B205-CD4F57860135}"/>
-    <hyperlink ref="M52" r:id="rId36" xr:uid="{5E0A0525-EF60-4BC3-816C-A0AF61B86230}"/>
-    <hyperlink ref="M53" r:id="rId37" xr:uid="{FBA91335-F556-49C3-8074-1B1FB90338FD}"/>
-    <hyperlink ref="M55" r:id="rId38" xr:uid="{1BA0974D-F2A5-4829-A486-BF96B8249301}"/>
-    <hyperlink ref="M73" r:id="rId39" xr:uid="{5A113D17-20D4-4ECC-A635-501B5C41F205}"/>
-    <hyperlink ref="M57" r:id="rId40" xr:uid="{FF006124-F785-4CEA-AFB9-38325E6F1CED}"/>
-    <hyperlink ref="M58" r:id="rId41" xr:uid="{64B6CE76-216E-455F-B948-EF8356A331AA}"/>
-    <hyperlink ref="M44" r:id="rId42" xr:uid="{497E408F-53E2-49B7-8F16-9DD7EA2ED202}"/>
-    <hyperlink ref="M38" r:id="rId43" location="sec2" xr:uid="{5034959D-6751-4851-84E0-172E272F75EE}"/>
-    <hyperlink ref="M40" r:id="rId44" xr:uid="{B7EB3734-AC4C-4151-A101-96D04051FDCD}"/>
-    <hyperlink ref="M41" r:id="rId45" xr:uid="{C91CD542-20C8-4FDA-BF4B-40DD95619963}"/>
-    <hyperlink ref="M37" r:id="rId46" location=":~:text=To%20comply%20with%20this%20purpose,protein%20production%20in%20microbial%20fermentations." xr:uid="{1A9C7341-CCC1-4312-91A0-12EA871608D9}"/>
-    <hyperlink ref="M39" r:id="rId47" xr:uid="{AA476111-326A-4868-8FB2-D9580E4ACE47}"/>
+    <hyperlink ref="M54" r:id="rId36" xr:uid="{5E0A0525-EF60-4BC3-816C-A0AF61B86230}"/>
+    <hyperlink ref="M55" r:id="rId37" xr:uid="{FBA91335-F556-49C3-8074-1B1FB90338FD}"/>
+    <hyperlink ref="M57" r:id="rId38" xr:uid="{1BA0974D-F2A5-4829-A486-BF96B8249301}"/>
+    <hyperlink ref="M75" r:id="rId39" xr:uid="{5A113D17-20D4-4ECC-A635-501B5C41F205}"/>
+    <hyperlink ref="M59" r:id="rId40" xr:uid="{FF006124-F785-4CEA-AFB9-38325E6F1CED}"/>
+    <hyperlink ref="M60" r:id="rId41" xr:uid="{64B6CE76-216E-455F-B948-EF8356A331AA}"/>
+    <hyperlink ref="M46" r:id="rId42" xr:uid="{497E408F-53E2-49B7-8F16-9DD7EA2ED202}"/>
+    <hyperlink ref="M40" r:id="rId43" location="sec2" xr:uid="{5034959D-6751-4851-84E0-172E272F75EE}"/>
+    <hyperlink ref="M42" r:id="rId44" xr:uid="{B7EB3734-AC4C-4151-A101-96D04051FDCD}"/>
+    <hyperlink ref="M43" r:id="rId45" xr:uid="{C91CD542-20C8-4FDA-BF4B-40DD95619963}"/>
+    <hyperlink ref="M39" r:id="rId46" location=":~:text=To%20comply%20with%20this%20purpose,protein%20production%20in%20microbial%20fermentations." xr:uid="{1A9C7341-CCC1-4312-91A0-12EA871608D9}"/>
+    <hyperlink ref="M41" r:id="rId47" xr:uid="{AA476111-326A-4868-8FB2-D9580E4ACE47}"/>
     <hyperlink ref="M35" r:id="rId48" xr:uid="{A35E98C5-C6A9-4A33-A079-EEED0DDD2B60}"/>
     <hyperlink ref="M36" r:id="rId49" location="fig0020" xr:uid="{0D4AA659-B49F-4D5C-9A30-E24621D94128}"/>
+    <hyperlink ref="M37" r:id="rId50" location="Sec18" xr:uid="{FFBE9CB1-C680-4B2B-81BA-60FEBB39DFC0}"/>
+    <hyperlink ref="M38" r:id="rId51" xr:uid="{1E73E7CA-B3FA-42E4-8201-C4C4BE351D65}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId50"/>
+  <pageSetup orientation="portrait" r:id="rId52"/>
 </worksheet>
 </file>
 

--- a/data/titre.xlsx
+++ b/data/titre.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pengb\PycharmProjects\protein_review\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E18DDDC-F902-4DE6-B016-FC84C6A004DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D8C3C21-ED1B-4F34-B019-A0F498500D67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="titre" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$M$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$M$62</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="704" uniqueCount="166">
   <si>
     <t>Candida boidinii</t>
   </si>
@@ -570,6 +570,9 @@
   </si>
   <si>
     <t>https://bioresourcesbioprocessing.springeropen.com/articles/10.1186/s40643-022-00606-3</t>
+  </si>
+  <si>
+    <t>https://analyticalsciencejournals.onlinelibrary.wiley.com/doi/full/10.1002/biot.70046</t>
   </si>
 </sst>
 </file>
@@ -961,7 +964,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M82"/>
+  <dimension ref="A1:M83"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.88671875" customWidth="1"/>
@@ -1806,7 +1809,7 @@
         <v>81</v>
       </c>
       <c r="K22">
-        <f t="shared" ref="K22:K38" si="3">I22/J22</f>
+        <f t="shared" ref="K22:K39" si="3">I22/J22</f>
         <v>5.5555555555555556E-4</v>
       </c>
       <c r="M22" s="1" t="s">
@@ -2216,7 +2219,7 @@
         <v>0.95833333333333337</v>
       </c>
       <c r="D33">
-        <f t="shared" ref="D33:D45" si="4">SUM(B33:C33)</f>
+        <f t="shared" ref="D33:D46" si="4">SUM(B33:C33)</f>
         <v>2024.9583333333333</v>
       </c>
       <c r="E33" t="s">
@@ -2409,7 +2412,7 @@
         <v>0.875</v>
       </c>
       <c r="D38">
-        <f t="shared" ref="D38" si="5">SUM(B38:C38)</f>
+        <f t="shared" ref="D38:D39" si="5">SUM(B38:C38)</f>
         <v>2022.875</v>
       </c>
       <c r="E38" t="s">
@@ -2436,42 +2439,43 @@
         <v>164</v>
       </c>
     </row>
-    <row r="39" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="10" t="s">
-        <v>157</v>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A39" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="B39">
-        <v>2010</v>
+        <v>2025</v>
       </c>
       <c r="C39">
-        <f>10.5/12</f>
-        <v>0.875</v>
+        <f>5.5/12</f>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D39">
-        <f t="shared" si="4"/>
-        <v>2010.875</v>
+        <f>SUM(B39:C39)</f>
+        <v>2025.4583333333333</v>
       </c>
       <c r="E39" t="s">
-        <v>39</v>
+        <v>106</v>
       </c>
       <c r="F39" t="s">
-        <v>140</v>
+        <v>106</v>
       </c>
       <c r="H39" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="I39">
-        <v>5.0999999999999996</v>
+        <v>0.63900000000000001</v>
       </c>
       <c r="J39">
-        <v>24.6</v>
+        <f>58*0.35</f>
+        <v>20.299999999999997</v>
       </c>
       <c r="K39">
-        <f t="shared" ref="K39:K42" si="6">I39/J39</f>
-        <v>0.20731707317073167</v>
+        <f t="shared" si="3"/>
+        <v>3.1477832512315278E-2</v>
       </c>
       <c r="M39" s="1" t="s">
-        <v>123</v>
+        <v>165</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -2479,15 +2483,15 @@
         <v>157</v>
       </c>
       <c r="B40">
-        <v>2007</v>
+        <v>2010</v>
       </c>
       <c r="C40">
-        <f>6.5/12</f>
-        <v>0.54166666666666663</v>
+        <f>10.5/12</f>
+        <v>0.875</v>
       </c>
       <c r="D40">
         <f t="shared" si="4"/>
-        <v>2007.5416666666667</v>
+        <v>2010.875</v>
       </c>
       <c r="E40" t="s">
         <v>39</v>
@@ -2499,17 +2503,17 @@
         <v>31</v>
       </c>
       <c r="I40">
-        <v>0.38500000000000001</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="J40">
-        <v>60</v>
+        <v>24.6</v>
       </c>
       <c r="K40">
-        <f t="shared" si="6"/>
-        <v>6.4166666666666669E-3</v>
+        <f t="shared" ref="K40:K43" si="6">I40/J40</f>
+        <v>0.20731707317073167</v>
       </c>
       <c r="M40" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -2517,37 +2521,37 @@
         <v>157</v>
       </c>
       <c r="B41">
-        <v>1999</v>
+        <v>2007</v>
       </c>
       <c r="C41">
-        <f>4.5/12</f>
-        <v>0.375</v>
+        <f>6.5/12</f>
+        <v>0.54166666666666663</v>
       </c>
       <c r="D41">
         <f t="shared" si="4"/>
-        <v>1999.375</v>
+        <v>2007.5416666666667</v>
       </c>
       <c r="E41" t="s">
-        <v>126</v>
+        <v>39</v>
       </c>
       <c r="F41" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="H41" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="I41">
-        <v>13.49</v>
+        <v>0.38500000000000001</v>
       </c>
       <c r="J41">
-        <v>125</v>
+        <v>60</v>
       </c>
       <c r="K41">
         <f t="shared" si="6"/>
-        <v>0.10792</v>
+        <v>6.4166666666666669E-3</v>
       </c>
       <c r="M41" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="42" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -2555,37 +2559,37 @@
         <v>157</v>
       </c>
       <c r="B42">
-        <v>2012</v>
+        <v>1999</v>
       </c>
       <c r="C42">
-        <f>11.5/12</f>
-        <v>0.95833333333333337</v>
+        <f>4.5/12</f>
+        <v>0.375</v>
       </c>
       <c r="D42">
         <f t="shared" si="4"/>
-        <v>2012.9583333333333</v>
+        <v>1999.375</v>
       </c>
       <c r="E42" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F42" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H42" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="I42">
-        <v>1.109</v>
+        <v>13.49</v>
       </c>
       <c r="J42">
-        <v>127.8</v>
+        <v>125</v>
       </c>
       <c r="K42">
         <f t="shared" si="6"/>
-        <v>8.677621283255086E-3</v>
+        <v>0.10792</v>
       </c>
       <c r="M42" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="43" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -2593,69 +2597,69 @@
         <v>157</v>
       </c>
       <c r="B43">
+        <v>2012</v>
+      </c>
+      <c r="C43">
+        <f>11.5/12</f>
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="D43">
+        <f t="shared" si="4"/>
+        <v>2012.9583333333333</v>
+      </c>
+      <c r="E43" t="s">
+        <v>127</v>
+      </c>
+      <c r="F43" t="s">
+        <v>127</v>
+      </c>
+      <c r="H43" t="s">
+        <v>31</v>
+      </c>
+      <c r="I43">
+        <v>1.109</v>
+      </c>
+      <c r="J43">
+        <v>127.8</v>
+      </c>
+      <c r="K43">
+        <f t="shared" si="6"/>
+        <v>8.677621283255086E-3</v>
+      </c>
+      <c r="M43" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A44" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="B44">
         <v>2016</v>
       </c>
-      <c r="C43">
+      <c r="C44">
         <f>4.5/12</f>
         <v>0.375</v>
       </c>
-      <c r="D43">
+      <c r="D44">
         <f t="shared" si="4"/>
         <v>2016.375</v>
       </c>
-      <c r="E43" t="s">
+      <c r="E44" t="s">
         <v>129</v>
       </c>
-      <c r="F43" t="s">
+      <c r="F44" t="s">
         <v>129</v>
       </c>
-      <c r="H43" t="s">
-        <v>10</v>
-      </c>
-      <c r="K43">
+      <c r="H44" t="s">
+        <v>10</v>
+      </c>
+      <c r="K44">
         <f>244.5*52000/1000000000</f>
         <v>1.2714E-2</v>
       </c>
-      <c r="M43" s="1" t="s">
+      <c r="M44" s="1" t="s">
         <v>130</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>0</v>
-      </c>
-      <c r="B44">
-        <v>1996</v>
-      </c>
-      <c r="C44">
-        <f>6.5/12</f>
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="D44">
-        <f t="shared" si="4"/>
-        <v>1996.5416666666667</v>
-      </c>
-      <c r="E44" t="s">
-        <v>6</v>
-      </c>
-      <c r="F44" t="s">
-        <v>88</v>
-      </c>
-      <c r="H44" t="s">
-        <v>10</v>
-      </c>
-      <c r="I44">
-        <v>3.5</v>
-      </c>
-      <c r="J44">
-        <v>90</v>
-      </c>
-      <c r="K44">
-        <f>I44/J44</f>
-        <v>3.888888888888889E-2</v>
-      </c>
-      <c r="M44" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.3">
@@ -2663,38 +2667,37 @@
         <v>0</v>
       </c>
       <c r="B45">
-        <v>2002</v>
+        <v>1996</v>
       </c>
       <c r="C45">
-        <f>5.5/12</f>
-        <v>0.45833333333333331</v>
+        <f>6.5/12</f>
+        <v>0.54166666666666663</v>
       </c>
       <c r="D45">
         <f t="shared" si="4"/>
-        <v>2002.4583333333333</v>
+        <v>1996.5416666666667</v>
       </c>
       <c r="E45" t="s">
-        <v>97</v>
+        <v>6</v>
       </c>
       <c r="F45" t="s">
-        <v>148</v>
+        <v>88</v>
       </c>
       <c r="H45" t="s">
         <v>10</v>
       </c>
       <c r="I45">
-        <v>1.2E-2</v>
+        <v>3.5</v>
       </c>
       <c r="J45">
-        <f>150*0.25</f>
-        <v>37.5</v>
+        <v>90</v>
       </c>
       <c r="K45">
         <f>I45/J45</f>
-        <v>3.2000000000000003E-4</v>
-      </c>
-      <c r="M45" t="s">
-        <v>98</v>
+        <v>3.888888888888889E-2</v>
+      </c>
+      <c r="M45" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.3">
@@ -2702,75 +2705,76 @@
         <v>0</v>
       </c>
       <c r="B46">
+        <v>2002</v>
+      </c>
+      <c r="C46">
+        <f>5.5/12</f>
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D46">
+        <f t="shared" si="4"/>
+        <v>2002.4583333333333</v>
+      </c>
+      <c r="E46" t="s">
+        <v>97</v>
+      </c>
+      <c r="F46" t="s">
+        <v>148</v>
+      </c>
+      <c r="H46" t="s">
+        <v>10</v>
+      </c>
+      <c r="I46">
+        <v>1.2E-2</v>
+      </c>
+      <c r="J46">
+        <f>150*0.25</f>
+        <v>37.5</v>
+      </c>
+      <c r="K46">
+        <f>I46/J46</f>
+        <v>3.2000000000000003E-4</v>
+      </c>
+      <c r="M46" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>0</v>
+      </c>
+      <c r="B47">
         <v>2004</v>
       </c>
-      <c r="C46">
+      <c r="C47">
         <f>6.5/12</f>
         <v>0.54166666666666663</v>
       </c>
-      <c r="D46">
-        <f t="shared" ref="D46" si="7">SUM(B46:C46)</f>
+      <c r="D47">
+        <f t="shared" ref="D47" si="7">SUM(B47:C47)</f>
         <v>2004.5416666666667</v>
       </c>
-      <c r="E46" t="s">
+      <c r="E47" t="s">
         <v>99</v>
       </c>
-      <c r="F46" t="s">
+      <c r="F47" t="s">
         <v>149</v>
       </c>
-      <c r="H46" t="s">
-        <v>31</v>
-      </c>
-      <c r="I46">
+      <c r="H47" t="s">
+        <v>31</v>
+      </c>
+      <c r="I47">
         <v>8.6999999999999994E-2</v>
       </c>
-      <c r="J46">
+      <c r="J47">
         <v>24</v>
-      </c>
-      <c r="K46">
-        <f>I46/J46</f>
-        <v>3.6249999999999998E-3</v>
-      </c>
-      <c r="M46" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>35</v>
-      </c>
-      <c r="B47">
-        <v>2022</v>
-      </c>
-      <c r="C47">
-        <f>2.5/12</f>
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="D47">
-        <f>SUM(B47:C47)</f>
-        <v>2022.2083333333333</v>
-      </c>
-      <c r="E47" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F47" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="H47" t="s">
-        <v>31</v>
-      </c>
-      <c r="I47">
-        <v>0.53</v>
-      </c>
-      <c r="J47">
-        <v>100</v>
       </c>
       <c r="K47">
         <f>I47/J47</f>
-        <v>5.3E-3</v>
+        <v>3.6249999999999998E-3</v>
       </c>
       <c r="M47" s="1" t="s">
-        <v>37</v>
+        <v>121</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.3">
@@ -2778,37 +2782,37 @@
         <v>35</v>
       </c>
       <c r="B48">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="C48">
-        <f>10.5/12</f>
-        <v>0.875</v>
+        <f>2.5/12</f>
+        <v>0.20833333333333334</v>
       </c>
       <c r="D48">
         <f>SUM(B48:C48)</f>
-        <v>2018.875</v>
-      </c>
-      <c r="E48" t="s">
-        <v>88</v>
-      </c>
-      <c r="F48" t="s">
-        <v>88</v>
+        <v>2022.2083333333333</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="H48" t="s">
         <v>31</v>
       </c>
-      <c r="I48" s="6">
-        <v>2.5</v>
-      </c>
-      <c r="J48" s="6">
-        <v>98.5</v>
+      <c r="I48">
+        <v>0.53</v>
+      </c>
+      <c r="J48">
+        <v>100</v>
       </c>
       <c r="K48">
         <f>I48/J48</f>
-        <v>2.5380710659898477E-2</v>
-      </c>
-      <c r="M48" t="s">
-        <v>89</v>
+        <v>5.3E-3</v>
+      </c>
+      <c r="M48" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.3">
@@ -2816,31 +2820,37 @@
         <v>35</v>
       </c>
       <c r="B49">
-        <v>2000</v>
+        <v>2018</v>
       </c>
       <c r="C49">
-        <f>1.5/12</f>
-        <v>0.125</v>
+        <f>10.5/12</f>
+        <v>0.875</v>
       </c>
       <c r="D49">
         <f>SUM(B49:C49)</f>
-        <v>2000.125</v>
+        <v>2018.875</v>
       </c>
       <c r="E49" t="s">
-        <v>12</v>
+        <v>88</v>
       </c>
       <c r="F49" t="s">
-        <v>12</v>
+        <v>88</v>
       </c>
       <c r="H49" t="s">
         <v>31</v>
       </c>
+      <c r="I49" s="6">
+        <v>2.5</v>
+      </c>
+      <c r="J49" s="6">
+        <v>98.5</v>
+      </c>
       <c r="K49">
-        <f>0.0093/0.4</f>
-        <v>2.3249999999999996E-2</v>
-      </c>
-      <c r="M49" s="1" t="s">
-        <v>90</v>
+        <f>I49/J49</f>
+        <v>2.5380710659898477E-2</v>
+      </c>
+      <c r="M49" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.3">
@@ -2848,30 +2858,31 @@
         <v>35</v>
       </c>
       <c r="B50">
-        <v>2013</v>
+        <v>2000</v>
       </c>
       <c r="C50">
-        <f>11.5/12</f>
-        <v>0.95833333333333337</v>
+        <f>1.5/12</f>
+        <v>0.125</v>
       </c>
       <c r="D50">
-        <f t="shared" ref="D50:D53" si="8">SUM(B50:C50)</f>
-        <v>2013.9583333333333</v>
+        <f>SUM(B50:C50)</f>
+        <v>2000.125</v>
       </c>
       <c r="E50" t="s">
-        <v>88</v>
+        <v>12</v>
       </c>
       <c r="F50" t="s">
-        <v>88</v>
+        <v>12</v>
       </c>
       <c r="H50" t="s">
         <v>31</v>
       </c>
       <c r="K50">
-        <v>1.4E-2</v>
-      </c>
-      <c r="M50" t="s">
-        <v>91</v>
+        <f>0.0093/0.4</f>
+        <v>2.3249999999999996E-2</v>
+      </c>
+      <c r="M50" s="1" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.3">
@@ -2879,27 +2890,27 @@
         <v>35</v>
       </c>
       <c r="B51">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="C51">
         <f>11.5/12</f>
         <v>0.95833333333333337</v>
       </c>
       <c r="D51">
-        <f t="shared" si="8"/>
-        <v>2012.9583333333333</v>
-      </c>
-      <c r="E51" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="F51" s="4" t="s">
-        <v>150</v>
+        <f t="shared" ref="D51:D54" si="8">SUM(B51:C51)</f>
+        <v>2013.9583333333333</v>
+      </c>
+      <c r="E51" t="s">
+        <v>88</v>
+      </c>
+      <c r="F51" t="s">
+        <v>88</v>
       </c>
       <c r="H51" t="s">
         <v>31</v>
       </c>
       <c r="K51">
-        <v>4.0000000000000001E-3</v>
+        <v>1.4E-2</v>
       </c>
       <c r="M51" t="s">
         <v>91</v>
@@ -2910,37 +2921,30 @@
         <v>35</v>
       </c>
       <c r="B52">
-        <v>2024</v>
+        <v>2012</v>
       </c>
       <c r="C52">
-        <f>7.5/12</f>
-        <v>0.625</v>
+        <f>11.5/12</f>
+        <v>0.95833333333333337</v>
       </c>
       <c r="D52">
         <f t="shared" si="8"/>
-        <v>2024.625</v>
-      </c>
-      <c r="E52" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="F52" s="7" t="s">
-        <v>93</v>
+        <v>2012.9583333333333</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>150</v>
       </c>
       <c r="H52" t="s">
         <v>31</v>
-      </c>
-      <c r="I52">
-        <v>0.11600000000000001</v>
-      </c>
-      <c r="J52">
-        <f>225*0.23</f>
-        <v>51.75</v>
       </c>
       <c r="K52">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="M52" s="1" t="s">
-        <v>94</v>
+      <c r="M52" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.3">
@@ -2948,102 +2952,101 @@
         <v>35</v>
       </c>
       <c r="B53">
+        <v>2024</v>
+      </c>
+      <c r="C53">
+        <f>7.5/12</f>
+        <v>0.625</v>
+      </c>
+      <c r="D53">
+        <f t="shared" si="8"/>
+        <v>2024.625</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="F53" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="H53" t="s">
+        <v>31</v>
+      </c>
+      <c r="I53">
+        <v>0.11600000000000001</v>
+      </c>
+      <c r="J53">
+        <f>225*0.23</f>
+        <v>51.75</v>
+      </c>
+      <c r="K53">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="M53" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>35</v>
+      </c>
+      <c r="B54">
         <v>2016</v>
       </c>
-      <c r="C53">
+      <c r="C54">
         <f>5.5/12</f>
         <v>0.45833333333333331</v>
       </c>
-      <c r="D53">
+      <c r="D54">
         <f t="shared" si="8"/>
         <v>2016.4583333333333</v>
       </c>
-      <c r="E53" t="s">
+      <c r="E54" t="s">
         <v>95</v>
       </c>
-      <c r="F53" t="s">
+      <c r="F54" t="s">
         <v>95</v>
       </c>
-      <c r="H53" t="s">
-        <v>31</v>
-      </c>
-      <c r="K53">
+      <c r="H54" t="s">
+        <v>31</v>
+      </c>
+      <c r="K54">
         <f>0.0002027/0.23</f>
         <v>8.8130434782608691E-4</v>
       </c>
-      <c r="M53" s="1" t="s">
+      <c r="M54" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
         <v>102</v>
       </c>
-      <c r="B54">
+      <c r="B55">
         <v>2022</v>
       </c>
-      <c r="C54">
+      <c r="C55">
         <f>6.5/12</f>
         <v>0.54166666666666663</v>
       </c>
-      <c r="D54">
-        <f t="shared" ref="D54" si="9">SUM(B54:C54)</f>
+      <c r="D55">
+        <f t="shared" ref="D55" si="9">SUM(B55:C55)</f>
         <v>2022.5416666666667</v>
       </c>
-      <c r="E54" s="8" t="s">
+      <c r="E55" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="F54" s="8" t="s">
+      <c r="F55" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="H54" t="s">
-        <v>31</v>
-      </c>
-      <c r="K54">
+      <c r="H55" t="s">
+        <v>31</v>
+      </c>
+      <c r="K55">
         <f>0.000349/0.35</f>
         <v>9.9714285714285725E-4</v>
       </c>
-      <c r="M54" s="1" t="s">
+      <c r="M55" s="1" t="s">
         <v>104</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
-        <v>105</v>
-      </c>
-      <c r="B55">
-        <v>2013</v>
-      </c>
-      <c r="C55">
-        <f>7.5/12</f>
-        <v>0.625</v>
-      </c>
-      <c r="D55">
-        <f t="shared" ref="D55:D61" si="10">SUM(B55:C55)</f>
-        <v>2013.625</v>
-      </c>
-      <c r="E55" t="s">
-        <v>106</v>
-      </c>
-      <c r="F55" t="s">
-        <v>106</v>
-      </c>
-      <c r="H55" t="s">
-        <v>31</v>
-      </c>
-      <c r="I55">
-        <v>0.104</v>
-      </c>
-      <c r="J55">
-        <f>40*0.51</f>
-        <v>20.399999999999999</v>
-      </c>
-      <c r="K55">
-        <f>I55/J55</f>
-        <v>5.0980392156862748E-3</v>
-      </c>
-      <c r="M55" s="1" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.3">
@@ -3051,38 +3054,38 @@
         <v>105</v>
       </c>
       <c r="B56">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="C56">
-        <f>11.5/12</f>
-        <v>0.95833333333333337</v>
+        <f>7.5/12</f>
+        <v>0.625</v>
       </c>
       <c r="D56">
-        <f t="shared" si="10"/>
-        <v>2014.9583333333333</v>
+        <f t="shared" ref="D56:D62" si="10">SUM(B56:C56)</f>
+        <v>2013.625</v>
       </c>
       <c r="E56" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="F56" t="s">
-        <v>134</v>
+        <v>106</v>
       </c>
       <c r="H56" t="s">
         <v>31</v>
       </c>
       <c r="I56">
-        <v>0.23699999999999999</v>
+        <v>0.104</v>
       </c>
       <c r="J56">
         <f>40*0.51</f>
         <v>20.399999999999999</v>
       </c>
       <c r="K56">
-        <f t="shared" ref="K56:K61" si="11">I56/J56</f>
-        <v>1.1617647058823529E-2</v>
+        <f>I56/J56</f>
+        <v>5.0980392156862748E-3</v>
       </c>
       <c r="M56" s="1" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.3">
@@ -3090,7 +3093,7 @@
         <v>105</v>
       </c>
       <c r="B57">
-        <v>2004</v>
+        <v>2014</v>
       </c>
       <c r="C57">
         <f>11.5/12</f>
@@ -3098,30 +3101,30 @@
       </c>
       <c r="D57">
         <f t="shared" si="10"/>
-        <v>2004.9583333333333</v>
+        <v>2014.9583333333333</v>
       </c>
       <c r="E57" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F57" t="s">
-        <v>151</v>
+        <v>134</v>
       </c>
       <c r="H57" t="s">
         <v>31</v>
       </c>
       <c r="I57">
-        <v>0.1</v>
+        <v>0.23699999999999999</v>
       </c>
       <c r="J57">
-        <f>20*0.51</f>
-        <v>10.199999999999999</v>
+        <f>40*0.51</f>
+        <v>20.399999999999999</v>
       </c>
       <c r="K57">
-        <f t="shared" si="11"/>
-        <v>9.8039215686274526E-3</v>
+        <f t="shared" ref="K57:K62" si="11">I57/J57</f>
+        <v>1.1617647058823529E-2</v>
       </c>
       <c r="M57" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.3">
@@ -3129,27 +3132,27 @@
         <v>105</v>
       </c>
       <c r="B58">
-        <v>1997</v>
+        <v>2004</v>
       </c>
       <c r="C58">
-        <f>7.5/12</f>
-        <v>0.625</v>
+        <f>11.5/12</f>
+        <v>0.95833333333333337</v>
       </c>
       <c r="D58">
         <f t="shared" si="10"/>
-        <v>1997.625</v>
+        <v>2004.9583333333333</v>
       </c>
       <c r="E58" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F58" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H58" t="s">
         <v>31</v>
       </c>
       <c r="I58">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="J58">
         <f>20*0.51</f>
@@ -3157,48 +3160,49 @@
       </c>
       <c r="K58">
         <f t="shared" si="11"/>
-        <v>1.2745098039215688E-2</v>
+        <v>9.8039215686274526E-3</v>
       </c>
       <c r="M58" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B59">
-        <v>1991</v>
+        <v>1997</v>
       </c>
       <c r="C59">
-        <f>9.5/12</f>
-        <v>0.79166666666666663</v>
+        <f>7.5/12</f>
+        <v>0.625</v>
       </c>
       <c r="D59">
         <f t="shared" si="10"/>
-        <v>1991.7916666666667</v>
+        <v>1997.625</v>
       </c>
       <c r="E59" t="s">
-        <v>39</v>
+        <v>116</v>
       </c>
       <c r="F59" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="H59" t="s">
         <v>31</v>
       </c>
       <c r="I59">
-        <v>0.29599999999999999</v>
+        <v>0.13</v>
       </c>
       <c r="J59">
-        <v>8</v>
+        <f>20*0.51</f>
+        <v>10.199999999999999</v>
       </c>
       <c r="K59">
         <f t="shared" si="11"/>
-        <v>3.6999999999999998E-2</v>
+        <v>1.2745098039215688E-2</v>
       </c>
       <c r="M59" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.3">
@@ -3206,7 +3210,7 @@
         <v>108</v>
       </c>
       <c r="B60">
-        <v>1994</v>
+        <v>1991</v>
       </c>
       <c r="C60">
         <f>9.5/12</f>
@@ -3214,7 +3218,7 @@
       </c>
       <c r="D60">
         <f t="shared" si="10"/>
-        <v>1994.7916666666667</v>
+        <v>1991.7916666666667</v>
       </c>
       <c r="E60" t="s">
         <v>39</v>
@@ -3223,140 +3227,161 @@
         <v>140</v>
       </c>
       <c r="H60" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="I60">
-        <v>6.2E-2</v>
+        <v>0.29599999999999999</v>
       </c>
       <c r="J60">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="K60">
         <f t="shared" si="11"/>
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="M60" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>108</v>
+      </c>
+      <c r="B61">
+        <v>1994</v>
+      </c>
+      <c r="C61">
+        <f>9.5/12</f>
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D61">
+        <f t="shared" si="10"/>
+        <v>1994.7916666666667</v>
+      </c>
+      <c r="E61" t="s">
+        <v>39</v>
+      </c>
+      <c r="F61" t="s">
+        <v>140</v>
+      </c>
+      <c r="H61" t="s">
+        <v>10</v>
+      </c>
+      <c r="I61">
+        <v>6.2E-2</v>
+      </c>
+      <c r="J61">
+        <v>35</v>
+      </c>
+      <c r="K61">
+        <f t="shared" si="11"/>
         <v>1.7714285714285714E-3</v>
       </c>
-      <c r="M60" s="1" t="s">
+      <c r="M61" s="1" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="61" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A61" s="10" t="s">
+    <row r="62" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A62" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="B61">
+      <c r="B62">
         <v>2025</v>
       </c>
-      <c r="C61">
+      <c r="C62">
         <f>11.5/12</f>
         <v>0.95833333333333337</v>
       </c>
-      <c r="D61">
+      <c r="D62">
         <f t="shared" si="10"/>
         <v>2025.9583333333333</v>
       </c>
-      <c r="E61" t="s">
+      <c r="E62" t="s">
         <v>154</v>
       </c>
-      <c r="F61" t="s">
+      <c r="F62" t="s">
         <v>154</v>
       </c>
-      <c r="H61" t="s">
-        <v>31</v>
-      </c>
-      <c r="I61">
+      <c r="H62" t="s">
+        <v>31</v>
+      </c>
+      <c r="I62">
         <v>3.456</v>
       </c>
-      <c r="J61">
+      <c r="J62">
         <f>316.3*0.35</f>
         <v>110.705</v>
       </c>
-      <c r="K61">
+      <c r="K62">
         <f t="shared" si="11"/>
         <v>3.1218102163407254E-2</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
         <v>131</v>
       </c>
-      <c r="M67" t="s">
+      <c r="M68" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
         <v>108</v>
       </c>
-      <c r="B75">
+      <c r="B76">
         <v>2024</v>
       </c>
-      <c r="C75">
+      <c r="C76">
         <f>2.5/12</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="D75">
-        <f>SUM(B75:C75)</f>
+      <c r="D76">
+        <f>SUM(B76:C76)</f>
         <v>2024.2083333333333</v>
       </c>
-      <c r="E75" t="s">
+      <c r="E76" t="s">
         <v>6</v>
       </c>
-      <c r="H75" t="s">
-        <v>10</v>
-      </c>
-      <c r="I75">
+      <c r="H76" t="s">
+        <v>10</v>
+      </c>
+      <c r="I76">
         <v>16.8</v>
       </c>
-      <c r="M75" s="1" t="s">
+      <c r="M76" s="1" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A76" s="9" t="s">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A77" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="I76">
+      <c r="I77">
         <v>0.08</v>
       </c>
-      <c r="M76" t="s">
+      <c r="M77" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="77" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A77" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B77">
+    <row r="78" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A78" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B78">
         <v>2023</v>
       </c>
-      <c r="E77" t="s">
+      <c r="E78" t="s">
         <v>12</v>
       </c>
-      <c r="H77" t="s">
-        <v>10</v>
-      </c>
-      <c r="I77">
+      <c r="H78" t="s">
+        <v>10</v>
+      </c>
+      <c r="I78">
         <v>3.7</v>
       </c>
-      <c r="M77" s="3" t="s">
+      <c r="M78" s="3" t="s">
         <v>63</v>
-      </c>
-    </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A78" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B78">
-        <v>2025</v>
-      </c>
-      <c r="E78" t="s">
-        <v>16</v>
-      </c>
-      <c r="L78" t="s">
-        <v>15</v>
-      </c>
-      <c r="M78" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.3">
@@ -3364,20 +3389,16 @@
         <v>11</v>
       </c>
       <c r="B79">
-        <v>2015</v>
-      </c>
-      <c r="E79" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="F79" s="4"/>
-      <c r="H79" t="s">
-        <v>31</v>
-      </c>
-      <c r="I79">
-        <v>0.2</v>
-      </c>
-      <c r="M79" t="s">
-        <v>69</v>
+        <v>2025</v>
+      </c>
+      <c r="E79" t="s">
+        <v>16</v>
+      </c>
+      <c r="L79" t="s">
+        <v>15</v>
+      </c>
+      <c r="M79" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.3">
@@ -3385,65 +3406,86 @@
         <v>11</v>
       </c>
       <c r="B80">
-        <v>1997</v>
-      </c>
-      <c r="E80" t="s">
-        <v>66</v>
-      </c>
+        <v>2015</v>
+      </c>
+      <c r="E80" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F80" s="4"/>
       <c r="H80" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="I80">
         <v>0.2</v>
       </c>
       <c r="M80" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A81" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B81">
+        <v>1997</v>
+      </c>
+      <c r="E81" t="s">
+        <v>66</v>
+      </c>
+      <c r="H81" t="s">
+        <v>10</v>
+      </c>
+      <c r="I81">
+        <v>0.2</v>
+      </c>
+      <c r="M81" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A81" t="s">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
         <v>105</v>
       </c>
-      <c r="B81">
+      <c r="B82">
         <v>1991</v>
       </c>
-      <c r="C81">
+      <c r="C82">
         <f>7.5/12</f>
         <v>0.625</v>
       </c>
-      <c r="D81">
-        <f>SUM(B81:C81)</f>
+      <c r="D82">
+        <f>SUM(B82:C82)</f>
         <v>1991.625</v>
       </c>
-      <c r="E81" t="s">
+      <c r="E82" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A82" t="s">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
         <v>108</v>
       </c>
-      <c r="B82">
+      <c r="B83">
         <v>1993</v>
       </c>
-      <c r="C82">
+      <c r="C83">
         <f>10.5/12</f>
         <v>0.875</v>
       </c>
-      <c r="D82">
-        <f t="shared" ref="D82" si="12">SUM(B82:C82)</f>
+      <c r="D83">
+        <f t="shared" ref="D83" si="12">SUM(B83:C83)</f>
         <v>1993.875</v>
       </c>
-      <c r="E82" t="s">
+      <c r="E83" t="s">
         <v>109</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M61" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:M62" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <hyperlinks>
-    <hyperlink ref="M44" r:id="rId1" xr:uid="{2C6F6E23-ECE2-48FD-9281-2D99D7593433}"/>
-    <hyperlink ref="M77" r:id="rId2" location="Sec2234" xr:uid="{62C0EF63-5AB8-4BA9-8B91-BED051CAB1BF}"/>
-    <hyperlink ref="M78" r:id="rId3" xr:uid="{B20578A3-8323-4DE4-85AE-68D7FF9E102B}"/>
+    <hyperlink ref="M45" r:id="rId1" xr:uid="{2C6F6E23-ECE2-48FD-9281-2D99D7593433}"/>
+    <hyperlink ref="M78" r:id="rId2" location="Sec2234" xr:uid="{62C0EF63-5AB8-4BA9-8B91-BED051CAB1BF}"/>
+    <hyperlink ref="M79" r:id="rId3" xr:uid="{B20578A3-8323-4DE4-85AE-68D7FF9E102B}"/>
     <hyperlink ref="M2" r:id="rId4" location="Sec2" xr:uid="{E3E93F9E-DE58-4D08-B99F-BCC6036F7008}"/>
     <hyperlink ref="M3" r:id="rId5" xr:uid="{D9A4AF65-DA70-469D-830F-18C855356D90}"/>
     <hyperlink ref="M4" r:id="rId6" xr:uid="{B12BC68D-68E4-4106-B5E4-E526B322A8A6}"/>
@@ -3471,30 +3513,31 @@
     <hyperlink ref="M11" r:id="rId28" xr:uid="{F4B38A8C-4738-4863-988E-62EDE0DDB3C8}"/>
     <hyperlink ref="M8" r:id="rId29" xr:uid="{EB34F27E-0B05-4195-B7F0-D388A7AD2D27}"/>
     <hyperlink ref="M6" r:id="rId30" xr:uid="{15DB38CB-6521-44E4-B260-EDC4586943ED}"/>
-    <hyperlink ref="M47" r:id="rId31" location="Sec2" xr:uid="{235DA6CA-59BB-493F-AE3F-01F1CACCC335}"/>
-    <hyperlink ref="M49" r:id="rId32" location="BIB8" xr:uid="{93BE3110-5F69-4CA6-9551-CCF063F7F511}"/>
-    <hyperlink ref="M52" r:id="rId33" xr:uid="{1DFC047B-89FD-4940-B346-4D1719C84B8D}"/>
-    <hyperlink ref="M53" r:id="rId34" location="Sec11" xr:uid="{CF173C6B-1889-4F7C-B611-E21261B20B04}"/>
+    <hyperlink ref="M48" r:id="rId31" location="Sec2" xr:uid="{235DA6CA-59BB-493F-AE3F-01F1CACCC335}"/>
+    <hyperlink ref="M50" r:id="rId32" location="BIB8" xr:uid="{93BE3110-5F69-4CA6-9551-CCF063F7F511}"/>
+    <hyperlink ref="M53" r:id="rId33" xr:uid="{1DFC047B-89FD-4940-B346-4D1719C84B8D}"/>
+    <hyperlink ref="M54" r:id="rId34" location="Sec11" xr:uid="{CF173C6B-1889-4F7C-B611-E21261B20B04}"/>
     <hyperlink ref="M34" r:id="rId35" xr:uid="{1D1CA4DD-57EB-4FDA-B205-CD4F57860135}"/>
-    <hyperlink ref="M54" r:id="rId36" xr:uid="{5E0A0525-EF60-4BC3-816C-A0AF61B86230}"/>
-    <hyperlink ref="M55" r:id="rId37" xr:uid="{FBA91335-F556-49C3-8074-1B1FB90338FD}"/>
-    <hyperlink ref="M57" r:id="rId38" xr:uid="{1BA0974D-F2A5-4829-A486-BF96B8249301}"/>
-    <hyperlink ref="M75" r:id="rId39" xr:uid="{5A113D17-20D4-4ECC-A635-501B5C41F205}"/>
-    <hyperlink ref="M59" r:id="rId40" xr:uid="{FF006124-F785-4CEA-AFB9-38325E6F1CED}"/>
-    <hyperlink ref="M60" r:id="rId41" xr:uid="{64B6CE76-216E-455F-B948-EF8356A331AA}"/>
-    <hyperlink ref="M46" r:id="rId42" xr:uid="{497E408F-53E2-49B7-8F16-9DD7EA2ED202}"/>
-    <hyperlink ref="M40" r:id="rId43" location="sec2" xr:uid="{5034959D-6751-4851-84E0-172E272F75EE}"/>
-    <hyperlink ref="M42" r:id="rId44" xr:uid="{B7EB3734-AC4C-4151-A101-96D04051FDCD}"/>
-    <hyperlink ref="M43" r:id="rId45" xr:uid="{C91CD542-20C8-4FDA-BF4B-40DD95619963}"/>
-    <hyperlink ref="M39" r:id="rId46" location=":~:text=To%20comply%20with%20this%20purpose,protein%20production%20in%20microbial%20fermentations." xr:uid="{1A9C7341-CCC1-4312-91A0-12EA871608D9}"/>
-    <hyperlink ref="M41" r:id="rId47" xr:uid="{AA476111-326A-4868-8FB2-D9580E4ACE47}"/>
+    <hyperlink ref="M55" r:id="rId36" xr:uid="{5E0A0525-EF60-4BC3-816C-A0AF61B86230}"/>
+    <hyperlink ref="M56" r:id="rId37" xr:uid="{FBA91335-F556-49C3-8074-1B1FB90338FD}"/>
+    <hyperlink ref="M58" r:id="rId38" xr:uid="{1BA0974D-F2A5-4829-A486-BF96B8249301}"/>
+    <hyperlink ref="M76" r:id="rId39" xr:uid="{5A113D17-20D4-4ECC-A635-501B5C41F205}"/>
+    <hyperlink ref="M60" r:id="rId40" xr:uid="{FF006124-F785-4CEA-AFB9-38325E6F1CED}"/>
+    <hyperlink ref="M61" r:id="rId41" xr:uid="{64B6CE76-216E-455F-B948-EF8356A331AA}"/>
+    <hyperlink ref="M47" r:id="rId42" xr:uid="{497E408F-53E2-49B7-8F16-9DD7EA2ED202}"/>
+    <hyperlink ref="M41" r:id="rId43" location="sec2" xr:uid="{5034959D-6751-4851-84E0-172E272F75EE}"/>
+    <hyperlink ref="M43" r:id="rId44" xr:uid="{B7EB3734-AC4C-4151-A101-96D04051FDCD}"/>
+    <hyperlink ref="M44" r:id="rId45" xr:uid="{C91CD542-20C8-4FDA-BF4B-40DD95619963}"/>
+    <hyperlink ref="M40" r:id="rId46" location=":~:text=To%20comply%20with%20this%20purpose,protein%20production%20in%20microbial%20fermentations." xr:uid="{1A9C7341-CCC1-4312-91A0-12EA871608D9}"/>
+    <hyperlink ref="M42" r:id="rId47" xr:uid="{AA476111-326A-4868-8FB2-D9580E4ACE47}"/>
     <hyperlink ref="M35" r:id="rId48" xr:uid="{A35E98C5-C6A9-4A33-A079-EEED0DDD2B60}"/>
     <hyperlink ref="M36" r:id="rId49" location="fig0020" xr:uid="{0D4AA659-B49F-4D5C-9A30-E24621D94128}"/>
     <hyperlink ref="M37" r:id="rId50" location="Sec18" xr:uid="{FFBE9CB1-C680-4B2B-81BA-60FEBB39DFC0}"/>
     <hyperlink ref="M38" r:id="rId51" xr:uid="{1E73E7CA-B3FA-42E4-8201-C4C4BE351D65}"/>
+    <hyperlink ref="M39" r:id="rId52" xr:uid="{12F65439-1071-4B8F-8FE6-E6BFC3AAEEAE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId52"/>
+  <pageSetup orientation="portrait" r:id="rId53"/>
 </worksheet>
 </file>
 

--- a/data/titre.xlsx
+++ b/data/titre.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pengb\PycharmProjects\protein_review\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pengb\PycharmProjects\productivity_secreted_protein\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D8C3C21-ED1B-4F34-B019-A0F498500D67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{820589F7-7C2F-4178-9C1C-695396C77651}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="titre" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$M$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$M$65</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="704" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="717" uniqueCount="168">
   <si>
     <t>Candida boidinii</t>
   </si>
@@ -573,6 +573,12 @@
   </si>
   <si>
     <t>https://analyticalsciencejournals.onlinelibrary.wiley.com/doi/full/10.1002/biot.70046</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/article/abs/pii/S1385894726039732?via%3Dihub</t>
+  </si>
+  <si>
+    <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13022228/</t>
   </si>
 </sst>
 </file>
@@ -964,7 +970,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M83"/>
+  <dimension ref="A1:M86"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.88671875" customWidth="1"/>
@@ -2219,7 +2225,7 @@
         <v>0.95833333333333337</v>
       </c>
       <c r="D33">
-        <f t="shared" ref="D33:D46" si="4">SUM(B33:C33)</f>
+        <f t="shared" ref="D33:D48" si="4">SUM(B33:C33)</f>
         <v>2024.9583333333333</v>
       </c>
       <c r="E33" t="s">
@@ -2412,7 +2418,7 @@
         <v>0.875</v>
       </c>
       <c r="D38">
-        <f t="shared" ref="D38:D39" si="5">SUM(B38:C38)</f>
+        <f t="shared" ref="D38" si="5">SUM(B38:C38)</f>
         <v>2022.875</v>
       </c>
       <c r="E38" t="s">
@@ -2478,80 +2484,69 @@
         <v>165</v>
       </c>
     </row>
-    <row r="40" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="10" t="s">
-        <v>157</v>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A40" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="B40">
-        <v>2010</v>
+        <v>2026</v>
       </c>
       <c r="C40">
-        <f>10.5/12</f>
-        <v>0.875</v>
+        <f>5.5/12</f>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D40">
-        <f t="shared" si="4"/>
-        <v>2010.875</v>
+        <f>SUM(B40:C40)</f>
+        <v>2026.4583333333333</v>
       </c>
       <c r="E40" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="F40" t="s">
-        <v>140</v>
+        <v>12</v>
       </c>
       <c r="H40" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="I40">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="J40">
-        <v>24.6</v>
+        <v>26.2</v>
       </c>
       <c r="K40">
-        <f t="shared" ref="K40:K43" si="6">I40/J40</f>
-        <v>0.20731707317073167</v>
+        <v>0.96899999999999997</v>
       </c>
       <c r="M40" s="1" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A41" s="10" t="s">
-        <v>157</v>
+        <v>166</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A41" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="B41">
-        <v>2007</v>
+        <v>2026</v>
       </c>
       <c r="C41">
-        <f>6.5/12</f>
-        <v>0.54166666666666663</v>
+        <f>2.5/12</f>
+        <v>0.20833333333333334</v>
       </c>
       <c r="D41">
-        <f t="shared" si="4"/>
-        <v>2007.5416666666667</v>
+        <f>SUM(B41:C41)</f>
+        <v>2026.2083333333333</v>
       </c>
       <c r="E41" t="s">
-        <v>39</v>
+        <v>162</v>
       </c>
       <c r="F41" t="s">
-        <v>140</v>
-      </c>
-      <c r="H41" t="s">
-        <v>31</v>
+        <v>162</v>
       </c>
       <c r="I41">
-        <v>0.38500000000000001</v>
-      </c>
-      <c r="J41">
-        <v>60</v>
+        <v>1.04</v>
       </c>
       <c r="K41">
-        <f t="shared" si="6"/>
-        <v>6.4166666666666669E-3</v>
+        <v>0.84</v>
       </c>
       <c r="M41" s="1" t="s">
-        <v>124</v>
+        <v>167</v>
       </c>
     </row>
     <row r="42" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -2559,37 +2554,37 @@
         <v>157</v>
       </c>
       <c r="B42">
-        <v>1999</v>
+        <v>2010</v>
       </c>
       <c r="C42">
-        <f>4.5/12</f>
-        <v>0.375</v>
+        <f>10.5/12</f>
+        <v>0.875</v>
       </c>
       <c r="D42">
         <f t="shared" si="4"/>
-        <v>1999.375</v>
+        <v>2010.875</v>
       </c>
       <c r="E42" t="s">
-        <v>126</v>
+        <v>39</v>
       </c>
       <c r="F42" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="H42" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="I42">
-        <v>13.49</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="J42">
-        <v>125</v>
+        <v>24.6</v>
       </c>
       <c r="K42">
-        <f t="shared" si="6"/>
-        <v>0.10792</v>
+        <f t="shared" ref="K42:K45" si="6">I42/J42</f>
+        <v>0.20731707317073167</v>
       </c>
       <c r="M42" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="43" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -2597,37 +2592,37 @@
         <v>157</v>
       </c>
       <c r="B43">
-        <v>2012</v>
+        <v>2007</v>
       </c>
       <c r="C43">
-        <f>11.5/12</f>
-        <v>0.95833333333333337</v>
+        <f>6.5/12</f>
+        <v>0.54166666666666663</v>
       </c>
       <c r="D43">
         <f t="shared" si="4"/>
-        <v>2012.9583333333333</v>
+        <v>2007.5416666666667</v>
       </c>
       <c r="E43" t="s">
-        <v>127</v>
+        <v>39</v>
       </c>
       <c r="F43" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="H43" t="s">
         <v>31</v>
       </c>
       <c r="I43">
-        <v>1.109</v>
+        <v>0.38500000000000001</v>
       </c>
       <c r="J43">
-        <v>127.8</v>
+        <v>60</v>
       </c>
       <c r="K43">
         <f t="shared" si="6"/>
-        <v>8.677621283255086E-3</v>
+        <v>6.4166666666666669E-3</v>
       </c>
       <c r="M43" s="1" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="44" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -2635,7 +2630,7 @@
         <v>157</v>
       </c>
       <c r="B44">
-        <v>2016</v>
+        <v>1999</v>
       </c>
       <c r="C44">
         <f>4.5/12</f>
@@ -2643,100 +2638,99 @@
       </c>
       <c r="D44">
         <f t="shared" si="4"/>
+        <v>1999.375</v>
+      </c>
+      <c r="E44" t="s">
+        <v>126</v>
+      </c>
+      <c r="F44" t="s">
+        <v>126</v>
+      </c>
+      <c r="H44" t="s">
+        <v>10</v>
+      </c>
+      <c r="I44">
+        <v>13.49</v>
+      </c>
+      <c r="J44">
+        <v>125</v>
+      </c>
+      <c r="K44">
+        <f t="shared" si="6"/>
+        <v>0.10792</v>
+      </c>
+      <c r="M44" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A45" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="B45">
+        <v>2012</v>
+      </c>
+      <c r="C45">
+        <f>11.5/12</f>
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="D45">
+        <f t="shared" si="4"/>
+        <v>2012.9583333333333</v>
+      </c>
+      <c r="E45" t="s">
+        <v>127</v>
+      </c>
+      <c r="F45" t="s">
+        <v>127</v>
+      </c>
+      <c r="H45" t="s">
+        <v>31</v>
+      </c>
+      <c r="I45">
+        <v>1.109</v>
+      </c>
+      <c r="J45">
+        <v>127.8</v>
+      </c>
+      <c r="K45">
+        <f t="shared" si="6"/>
+        <v>8.677621283255086E-3</v>
+      </c>
+      <c r="M45" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A46" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="B46">
+        <v>2016</v>
+      </c>
+      <c r="C46">
+        <f>4.5/12</f>
+        <v>0.375</v>
+      </c>
+      <c r="D46">
+        <f t="shared" si="4"/>
         <v>2016.375</v>
       </c>
-      <c r="E44" t="s">
+      <c r="E46" t="s">
         <v>129</v>
       </c>
-      <c r="F44" t="s">
+      <c r="F46" t="s">
         <v>129</v>
       </c>
-      <c r="H44" t="s">
-        <v>10</v>
-      </c>
-      <c r="K44">
+      <c r="H46" t="s">
+        <v>10</v>
+      </c>
+      <c r="K46">
         <f>244.5*52000/1000000000</f>
         <v>1.2714E-2</v>
       </c>
-      <c r="M44" s="1" t="s">
+      <c r="M46" s="1" t="s">
         <v>130</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>0</v>
-      </c>
-      <c r="B45">
-        <v>1996</v>
-      </c>
-      <c r="C45">
-        <f>6.5/12</f>
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="D45">
-        <f t="shared" si="4"/>
-        <v>1996.5416666666667</v>
-      </c>
-      <c r="E45" t="s">
-        <v>6</v>
-      </c>
-      <c r="F45" t="s">
-        <v>88</v>
-      </c>
-      <c r="H45" t="s">
-        <v>10</v>
-      </c>
-      <c r="I45">
-        <v>3.5</v>
-      </c>
-      <c r="J45">
-        <v>90</v>
-      </c>
-      <c r="K45">
-        <f>I45/J45</f>
-        <v>3.888888888888889E-2</v>
-      </c>
-      <c r="M45" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>0</v>
-      </c>
-      <c r="B46">
-        <v>2002</v>
-      </c>
-      <c r="C46">
-        <f>5.5/12</f>
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D46">
-        <f t="shared" si="4"/>
-        <v>2002.4583333333333</v>
-      </c>
-      <c r="E46" t="s">
-        <v>97</v>
-      </c>
-      <c r="F46" t="s">
-        <v>148</v>
-      </c>
-      <c r="H46" t="s">
-        <v>10</v>
-      </c>
-      <c r="I46">
-        <v>1.2E-2</v>
-      </c>
-      <c r="J46">
-        <f>150*0.25</f>
-        <v>37.5</v>
-      </c>
-      <c r="K46">
-        <f>I46/J46</f>
-        <v>3.2000000000000003E-4</v>
-      </c>
-      <c r="M46" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.3">
@@ -2744,113 +2738,114 @@
         <v>0</v>
       </c>
       <c r="B47">
-        <v>2004</v>
+        <v>1996</v>
       </c>
       <c r="C47">
         <f>6.5/12</f>
         <v>0.54166666666666663</v>
       </c>
       <c r="D47">
-        <f t="shared" ref="D47" si="7">SUM(B47:C47)</f>
-        <v>2004.5416666666667</v>
+        <f t="shared" si="4"/>
+        <v>1996.5416666666667</v>
       </c>
       <c r="E47" t="s">
-        <v>99</v>
+        <v>6</v>
       </c>
       <c r="F47" t="s">
-        <v>149</v>
+        <v>88</v>
       </c>
       <c r="H47" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="I47">
-        <v>8.6999999999999994E-2</v>
+        <v>3.5</v>
       </c>
       <c r="J47">
-        <v>24</v>
+        <v>90</v>
       </c>
       <c r="K47">
         <f>I47/J47</f>
-        <v>3.6249999999999998E-3</v>
+        <v>3.888888888888889E-2</v>
       </c>
       <c r="M47" s="1" t="s">
-        <v>121</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="B48">
-        <v>2022</v>
+        <v>2002</v>
       </c>
       <c r="C48">
-        <f>2.5/12</f>
-        <v>0.20833333333333334</v>
+        <f>5.5/12</f>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D48">
-        <f>SUM(B48:C48)</f>
-        <v>2022.2083333333333</v>
-      </c>
-      <c r="E48" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F48" s="4" t="s">
-        <v>36</v>
+        <f t="shared" si="4"/>
+        <v>2002.4583333333333</v>
+      </c>
+      <c r="E48" t="s">
+        <v>97</v>
+      </c>
+      <c r="F48" t="s">
+        <v>148</v>
       </c>
       <c r="H48" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="I48">
-        <v>0.53</v>
+        <v>1.2E-2</v>
       </c>
       <c r="J48">
-        <v>100</v>
+        <f>150*0.25</f>
+        <v>37.5</v>
       </c>
       <c r="K48">
         <f>I48/J48</f>
-        <v>5.3E-3</v>
-      </c>
-      <c r="M48" s="1" t="s">
-        <v>37</v>
+        <v>3.2000000000000003E-4</v>
+      </c>
+      <c r="M48" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="B49">
-        <v>2018</v>
+        <v>2004</v>
       </c>
       <c r="C49">
-        <f>10.5/12</f>
-        <v>0.875</v>
+        <f>6.5/12</f>
+        <v>0.54166666666666663</v>
       </c>
       <c r="D49">
-        <f>SUM(B49:C49)</f>
-        <v>2018.875</v>
+        <f t="shared" ref="D49" si="7">SUM(B49:C49)</f>
+        <v>2004.5416666666667</v>
       </c>
       <c r="E49" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="F49" t="s">
-        <v>88</v>
+        <v>149</v>
       </c>
       <c r="H49" t="s">
         <v>31</v>
       </c>
-      <c r="I49" s="6">
-        <v>2.5</v>
-      </c>
-      <c r="J49" s="6">
-        <v>98.5</v>
+      <c r="I49">
+        <v>8.6999999999999994E-2</v>
+      </c>
+      <c r="J49">
+        <v>24</v>
       </c>
       <c r="K49">
         <f>I49/J49</f>
-        <v>2.5380710659898477E-2</v>
-      </c>
-      <c r="M49" t="s">
-        <v>89</v>
+        <v>3.6249999999999998E-3</v>
+      </c>
+      <c r="M49" s="1" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.3">
@@ -2858,31 +2853,37 @@
         <v>35</v>
       </c>
       <c r="B50">
-        <v>2000</v>
+        <v>2022</v>
       </c>
       <c r="C50">
-        <f>1.5/12</f>
-        <v>0.125</v>
+        <f>2.5/12</f>
+        <v>0.20833333333333334</v>
       </c>
       <c r="D50">
         <f>SUM(B50:C50)</f>
-        <v>2000.125</v>
-      </c>
-      <c r="E50" t="s">
-        <v>12</v>
-      </c>
-      <c r="F50" t="s">
-        <v>12</v>
+        <v>2022.2083333333333</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="H50" t="s">
         <v>31</v>
       </c>
+      <c r="I50">
+        <v>0.53</v>
+      </c>
+      <c r="J50">
+        <v>100</v>
+      </c>
       <c r="K50">
-        <f>0.0093/0.4</f>
-        <v>2.3249999999999996E-2</v>
+        <f>I50/J50</f>
+        <v>5.3E-3</v>
       </c>
       <c r="M50" s="1" t="s">
-        <v>90</v>
+        <v>37</v>
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.3">
@@ -2890,15 +2891,15 @@
         <v>35</v>
       </c>
       <c r="B51">
-        <v>2013</v>
+        <v>2018</v>
       </c>
       <c r="C51">
-        <f>11.5/12</f>
-        <v>0.95833333333333337</v>
+        <f>10.5/12</f>
+        <v>0.875</v>
       </c>
       <c r="D51">
-        <f t="shared" ref="D51:D54" si="8">SUM(B51:C51)</f>
-        <v>2013.9583333333333</v>
+        <f>SUM(B51:C51)</f>
+        <v>2018.875</v>
       </c>
       <c r="E51" t="s">
         <v>88</v>
@@ -2909,11 +2910,18 @@
       <c r="H51" t="s">
         <v>31</v>
       </c>
+      <c r="I51" s="6">
+        <v>2.5</v>
+      </c>
+      <c r="J51" s="6">
+        <v>98.5</v>
+      </c>
       <c r="K51">
-        <v>1.4E-2</v>
+        <f>I51/J51</f>
+        <v>2.5380710659898477E-2</v>
       </c>
       <c r="M51" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.3">
@@ -2921,30 +2929,31 @@
         <v>35</v>
       </c>
       <c r="B52">
-        <v>2012</v>
+        <v>2000</v>
       </c>
       <c r="C52">
-        <f>11.5/12</f>
-        <v>0.95833333333333337</v>
+        <f>1.5/12</f>
+        <v>0.125</v>
       </c>
       <c r="D52">
-        <f t="shared" si="8"/>
-        <v>2012.9583333333333</v>
-      </c>
-      <c r="E52" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="F52" s="4" t="s">
-        <v>150</v>
+        <f>SUM(B52:C52)</f>
+        <v>2000.125</v>
+      </c>
+      <c r="E52" t="s">
+        <v>12</v>
+      </c>
+      <c r="F52" t="s">
+        <v>12</v>
       </c>
       <c r="H52" t="s">
         <v>31</v>
       </c>
       <c r="K52">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="M52" t="s">
-        <v>91</v>
+        <f>0.0093/0.4</f>
+        <v>2.3249999999999996E-2</v>
+      </c>
+      <c r="M52" s="1" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.3">
@@ -2952,37 +2961,30 @@
         <v>35</v>
       </c>
       <c r="B53">
-        <v>2024</v>
+        <v>2013</v>
       </c>
       <c r="C53">
-        <f>7.5/12</f>
-        <v>0.625</v>
+        <f>11.5/12</f>
+        <v>0.95833333333333337</v>
       </c>
       <c r="D53">
-        <f t="shared" si="8"/>
-        <v>2024.625</v>
-      </c>
-      <c r="E53" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="F53" s="7" t="s">
-        <v>93</v>
+        <f t="shared" ref="D53:D57" si="8">SUM(B53:C53)</f>
+        <v>2013.9583333333333</v>
+      </c>
+      <c r="E53" t="s">
+        <v>88</v>
+      </c>
+      <c r="F53" t="s">
+        <v>88</v>
       </c>
       <c r="H53" t="s">
         <v>31</v>
       </c>
-      <c r="I53">
-        <v>0.11600000000000001</v>
-      </c>
-      <c r="J53">
-        <f>225*0.23</f>
-        <v>51.75</v>
-      </c>
       <c r="K53">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="M53" s="1" t="s">
-        <v>94</v>
+        <v>1.4E-2</v>
+      </c>
+      <c r="M53" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.3">
@@ -2990,180 +2992,165 @@
         <v>35</v>
       </c>
       <c r="B54">
+        <v>2012</v>
+      </c>
+      <c r="C54">
+        <f>11.5/12</f>
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="D54">
+        <f t="shared" si="8"/>
+        <v>2012.9583333333333</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="H54" t="s">
+        <v>31</v>
+      </c>
+      <c r="K54">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="M54" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>35</v>
+      </c>
+      <c r="B55">
+        <v>2024</v>
+      </c>
+      <c r="C55">
+        <f>7.5/12</f>
+        <v>0.625</v>
+      </c>
+      <c r="D55">
+        <f t="shared" si="8"/>
+        <v>2024.625</v>
+      </c>
+      <c r="E55" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="F55" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="H55" t="s">
+        <v>31</v>
+      </c>
+      <c r="I55">
+        <v>0.11600000000000001</v>
+      </c>
+      <c r="J55">
+        <f>225*0.23</f>
+        <v>51.75</v>
+      </c>
+      <c r="K55">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="M55" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>35</v>
+      </c>
+      <c r="B56">
         <v>2016</v>
       </c>
-      <c r="C54">
+      <c r="C56">
         <f>5.5/12</f>
         <v>0.45833333333333331</v>
       </c>
-      <c r="D54">
+      <c r="D56">
         <f t="shared" si="8"/>
         <v>2016.4583333333333</v>
       </c>
-      <c r="E54" t="s">
+      <c r="E56" t="s">
         <v>95</v>
       </c>
-      <c r="F54" t="s">
+      <c r="F56" t="s">
         <v>95</v>
       </c>
-      <c r="H54" t="s">
-        <v>31</v>
-      </c>
-      <c r="K54">
+      <c r="H56" t="s">
+        <v>31</v>
+      </c>
+      <c r="K56">
         <f>0.0002027/0.23</f>
         <v>8.8130434782608691E-4</v>
       </c>
-      <c r="M54" s="1" t="s">
+      <c r="M56" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>35</v>
+      </c>
+      <c r="B57">
+        <v>2026</v>
+      </c>
+      <c r="C57">
+        <f>1.5/12</f>
+        <v>0.125</v>
+      </c>
+      <c r="D57">
+        <f t="shared" si="8"/>
+        <v>2026.125</v>
+      </c>
+      <c r="E57" t="s">
+        <v>88</v>
+      </c>
+      <c r="F57" t="s">
+        <v>88</v>
+      </c>
+      <c r="H57" t="s">
+        <v>31</v>
+      </c>
+      <c r="I57">
+        <v>6.6</v>
+      </c>
+      <c r="K57">
+        <f>6.6/(120*4.93/7.79)</f>
+        <v>8.6906693711967561E-2</v>
+      </c>
+      <c r="M57" s="1"/>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
         <v>102</v>
       </c>
-      <c r="B55">
+      <c r="B58">
         <v>2022</v>
       </c>
-      <c r="C55">
+      <c r="C58">
         <f>6.5/12</f>
         <v>0.54166666666666663</v>
       </c>
-      <c r="D55">
-        <f t="shared" ref="D55" si="9">SUM(B55:C55)</f>
+      <c r="D58">
+        <f t="shared" ref="D58" si="9">SUM(B58:C58)</f>
         <v>2022.5416666666667</v>
       </c>
-      <c r="E55" s="8" t="s">
+      <c r="E58" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="F55" s="8" t="s">
+      <c r="F58" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="H55" t="s">
-        <v>31</v>
-      </c>
-      <c r="K55">
+      <c r="H58" t="s">
+        <v>31</v>
+      </c>
+      <c r="K58">
         <f>0.000349/0.35</f>
         <v>9.9714285714285725E-4</v>
       </c>
-      <c r="M55" s="1" t="s">
+      <c r="M58" s="1" t="s">
         <v>104</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>105</v>
-      </c>
-      <c r="B56">
-        <v>2013</v>
-      </c>
-      <c r="C56">
-        <f>7.5/12</f>
-        <v>0.625</v>
-      </c>
-      <c r="D56">
-        <f t="shared" ref="D56:D62" si="10">SUM(B56:C56)</f>
-        <v>2013.625</v>
-      </c>
-      <c r="E56" t="s">
-        <v>106</v>
-      </c>
-      <c r="F56" t="s">
-        <v>106</v>
-      </c>
-      <c r="H56" t="s">
-        <v>31</v>
-      </c>
-      <c r="I56">
-        <v>0.104</v>
-      </c>
-      <c r="J56">
-        <f>40*0.51</f>
-        <v>20.399999999999999</v>
-      </c>
-      <c r="K56">
-        <f>I56/J56</f>
-        <v>5.0980392156862748E-3</v>
-      </c>
-      <c r="M56" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>105</v>
-      </c>
-      <c r="B57">
-        <v>2014</v>
-      </c>
-      <c r="C57">
-        <f>11.5/12</f>
-        <v>0.95833333333333337</v>
-      </c>
-      <c r="D57">
-        <f t="shared" si="10"/>
-        <v>2014.9583333333333</v>
-      </c>
-      <c r="E57" t="s">
-        <v>112</v>
-      </c>
-      <c r="F57" t="s">
-        <v>134</v>
-      </c>
-      <c r="H57" t="s">
-        <v>31</v>
-      </c>
-      <c r="I57">
-        <v>0.23699999999999999</v>
-      </c>
-      <c r="J57">
-        <f>40*0.51</f>
-        <v>20.399999999999999</v>
-      </c>
-      <c r="K57">
-        <f t="shared" ref="K57:K62" si="11">I57/J57</f>
-        <v>1.1617647058823529E-2</v>
-      </c>
-      <c r="M57" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>105</v>
-      </c>
-      <c r="B58">
-        <v>2004</v>
-      </c>
-      <c r="C58">
-        <f>11.5/12</f>
-        <v>0.95833333333333337</v>
-      </c>
-      <c r="D58">
-        <f t="shared" si="10"/>
-        <v>2004.9583333333333</v>
-      </c>
-      <c r="E58" t="s">
-        <v>114</v>
-      </c>
-      <c r="F58" t="s">
-        <v>151</v>
-      </c>
-      <c r="H58" t="s">
-        <v>31</v>
-      </c>
-      <c r="I58">
-        <v>0.1</v>
-      </c>
-      <c r="J58">
-        <f>20*0.51</f>
-        <v>10.199999999999999</v>
-      </c>
-      <c r="K58">
-        <f t="shared" si="11"/>
-        <v>9.8039215686274526E-3</v>
-      </c>
-      <c r="M58" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.3">
@@ -3171,321 +3158,438 @@
         <v>105</v>
       </c>
       <c r="B59">
-        <v>1997</v>
+        <v>2013</v>
       </c>
       <c r="C59">
         <f>7.5/12</f>
         <v>0.625</v>
       </c>
       <c r="D59">
+        <f t="shared" ref="D59:D65" si="10">SUM(B59:C59)</f>
+        <v>2013.625</v>
+      </c>
+      <c r="E59" t="s">
+        <v>106</v>
+      </c>
+      <c r="F59" t="s">
+        <v>106</v>
+      </c>
+      <c r="H59" t="s">
+        <v>31</v>
+      </c>
+      <c r="I59">
+        <v>0.104</v>
+      </c>
+      <c r="J59">
+        <f>40*0.51</f>
+        <v>20.399999999999999</v>
+      </c>
+      <c r="K59">
+        <f>I59/J59</f>
+        <v>5.0980392156862748E-3</v>
+      </c>
+      <c r="M59" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>105</v>
+      </c>
+      <c r="B60">
+        <v>2014</v>
+      </c>
+      <c r="C60">
+        <f>11.5/12</f>
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="D60">
+        <f t="shared" si="10"/>
+        <v>2014.9583333333333</v>
+      </c>
+      <c r="E60" t="s">
+        <v>112</v>
+      </c>
+      <c r="F60" t="s">
+        <v>134</v>
+      </c>
+      <c r="H60" t="s">
+        <v>31</v>
+      </c>
+      <c r="I60">
+        <v>0.23699999999999999</v>
+      </c>
+      <c r="J60">
+        <f>40*0.51</f>
+        <v>20.399999999999999</v>
+      </c>
+      <c r="K60">
+        <f t="shared" ref="K60:K65" si="11">I60/J60</f>
+        <v>1.1617647058823529E-2</v>
+      </c>
+      <c r="M60" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>105</v>
+      </c>
+      <c r="B61">
+        <v>2004</v>
+      </c>
+      <c r="C61">
+        <f>11.5/12</f>
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="D61">
+        <f t="shared" si="10"/>
+        <v>2004.9583333333333</v>
+      </c>
+      <c r="E61" t="s">
+        <v>114</v>
+      </c>
+      <c r="F61" t="s">
+        <v>151</v>
+      </c>
+      <c r="H61" t="s">
+        <v>31</v>
+      </c>
+      <c r="I61">
+        <v>0.1</v>
+      </c>
+      <c r="J61">
+        <f>20*0.51</f>
+        <v>10.199999999999999</v>
+      </c>
+      <c r="K61">
+        <f t="shared" si="11"/>
+        <v>9.8039215686274526E-3</v>
+      </c>
+      <c r="M61" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>105</v>
+      </c>
+      <c r="B62">
+        <v>1997</v>
+      </c>
+      <c r="C62">
+        <f>7.5/12</f>
+        <v>0.625</v>
+      </c>
+      <c r="D62">
         <f t="shared" si="10"/>
         <v>1997.625</v>
       </c>
-      <c r="E59" t="s">
+      <c r="E62" t="s">
         <v>116</v>
       </c>
-      <c r="F59" t="s">
+      <c r="F62" t="s">
         <v>152</v>
       </c>
-      <c r="H59" t="s">
-        <v>31</v>
-      </c>
-      <c r="I59">
+      <c r="H62" t="s">
+        <v>31</v>
+      </c>
+      <c r="I62">
         <v>0.13</v>
       </c>
-      <c r="J59">
+      <c r="J62">
         <f>20*0.51</f>
         <v>10.199999999999999</v>
       </c>
-      <c r="K59">
+      <c r="K62">
         <f t="shared" si="11"/>
         <v>1.2745098039215688E-2</v>
       </c>
-      <c r="M59" s="1" t="s">
+      <c r="M62" s="1" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
         <v>108</v>
       </c>
-      <c r="B60">
+      <c r="B63">
         <v>1991</v>
       </c>
-      <c r="C60">
+      <c r="C63">
         <f>9.5/12</f>
         <v>0.79166666666666663</v>
       </c>
-      <c r="D60">
+      <c r="D63">
         <f t="shared" si="10"/>
         <v>1991.7916666666667</v>
       </c>
-      <c r="E60" t="s">
+      <c r="E63" t="s">
         <v>39</v>
       </c>
-      <c r="F60" t="s">
+      <c r="F63" t="s">
         <v>140</v>
       </c>
-      <c r="H60" t="s">
-        <v>31</v>
-      </c>
-      <c r="I60">
+      <c r="H63" t="s">
+        <v>31</v>
+      </c>
+      <c r="I63">
         <v>0.29599999999999999</v>
       </c>
-      <c r="J60">
+      <c r="J63">
         <v>8</v>
       </c>
-      <c r="K60">
+      <c r="K63">
         <f t="shared" si="11"/>
         <v>3.6999999999999998E-2</v>
       </c>
-      <c r="M60" s="1" t="s">
+      <c r="M63" s="1" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
         <v>108</v>
       </c>
-      <c r="B61">
+      <c r="B64">
         <v>1994</v>
       </c>
-      <c r="C61">
+      <c r="C64">
         <f>9.5/12</f>
         <v>0.79166666666666663</v>
       </c>
-      <c r="D61">
+      <c r="D64">
         <f t="shared" si="10"/>
         <v>1994.7916666666667</v>
       </c>
-      <c r="E61" t="s">
+      <c r="E64" t="s">
         <v>39</v>
       </c>
-      <c r="F61" t="s">
+      <c r="F64" t="s">
         <v>140</v>
       </c>
-      <c r="H61" t="s">
-        <v>10</v>
-      </c>
-      <c r="I61">
+      <c r="H64" t="s">
+        <v>10</v>
+      </c>
+      <c r="I64">
         <v>6.2E-2</v>
       </c>
-      <c r="J61">
+      <c r="J64">
         <v>35</v>
       </c>
-      <c r="K61">
+      <c r="K64">
         <f t="shared" si="11"/>
         <v>1.7714285714285714E-3</v>
       </c>
-      <c r="M61" s="1" t="s">
+      <c r="M64" s="1" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="62" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A62" s="10" t="s">
+    <row r="65" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A65" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="B62">
+      <c r="B65">
         <v>2025</v>
       </c>
-      <c r="C62">
+      <c r="C65">
         <f>11.5/12</f>
         <v>0.95833333333333337</v>
       </c>
-      <c r="D62">
+      <c r="D65">
         <f t="shared" si="10"/>
         <v>2025.9583333333333</v>
       </c>
-      <c r="E62" t="s">
+      <c r="E65" t="s">
         <v>154</v>
       </c>
-      <c r="F62" t="s">
+      <c r="F65" t="s">
         <v>154</v>
       </c>
-      <c r="H62" t="s">
-        <v>31</v>
-      </c>
-      <c r="I62">
+      <c r="H65" t="s">
+        <v>31</v>
+      </c>
+      <c r="I65">
         <v>3.456</v>
       </c>
-      <c r="J62">
+      <c r="J65">
         <f>316.3*0.35</f>
         <v>110.705</v>
       </c>
-      <c r="K62">
+      <c r="K65">
         <f t="shared" si="11"/>
         <v>3.1218102163407254E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
         <v>131</v>
       </c>
-      <c r="M68" t="s">
+      <c r="M71" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
         <v>108</v>
       </c>
-      <c r="B76">
+      <c r="B79">
         <v>2024</v>
       </c>
-      <c r="C76">
+      <c r="C79">
         <f>2.5/12</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="D76">
-        <f>SUM(B76:C76)</f>
+      <c r="D79">
+        <f>SUM(B79:C79)</f>
         <v>2024.2083333333333</v>
       </c>
-      <c r="E76" t="s">
+      <c r="E79" t="s">
         <v>6</v>
       </c>
-      <c r="H76" t="s">
-        <v>10</v>
-      </c>
-      <c r="I76">
+      <c r="H79" t="s">
+        <v>10</v>
+      </c>
+      <c r="I79">
         <v>16.8</v>
       </c>
-      <c r="M76" s="1" t="s">
+      <c r="M79" s="1" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A77" s="9" t="s">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A80" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="I77">
+      <c r="I80">
         <v>0.08</v>
       </c>
-      <c r="M77" t="s">
+      <c r="M80" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="78" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A78" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B78">
+    <row r="81" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A81" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B81">
         <v>2023</v>
       </c>
-      <c r="E78" t="s">
+      <c r="E81" t="s">
         <v>12</v>
       </c>
-      <c r="H78" t="s">
-        <v>10</v>
-      </c>
-      <c r="I78">
+      <c r="H81" t="s">
+        <v>10</v>
+      </c>
+      <c r="I81">
         <v>3.7</v>
       </c>
-      <c r="M78" s="3" t="s">
+      <c r="M81" s="3" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A79" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B79">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A82" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B82">
         <v>2025</v>
       </c>
-      <c r="E79" t="s">
+      <c r="E82" t="s">
         <v>16</v>
       </c>
-      <c r="L79" t="s">
+      <c r="L82" t="s">
         <v>15</v>
       </c>
-      <c r="M79" s="1" t="s">
+      <c r="M82" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A80" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B80">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A83" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B83">
         <v>2015</v>
       </c>
-      <c r="E80" s="4" t="s">
+      <c r="E83" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="F80" s="4"/>
-      <c r="H80" t="s">
-        <v>31</v>
-      </c>
-      <c r="I80">
+      <c r="F83" s="4"/>
+      <c r="H83" t="s">
+        <v>31</v>
+      </c>
+      <c r="I83">
         <v>0.2</v>
       </c>
-      <c r="M80" t="s">
+      <c r="M83" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A81" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B81">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A84" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B84">
         <v>1997</v>
       </c>
-      <c r="E81" t="s">
+      <c r="E84" t="s">
         <v>66</v>
       </c>
-      <c r="H81" t="s">
-        <v>10</v>
-      </c>
-      <c r="I81">
+      <c r="H84" t="s">
+        <v>10</v>
+      </c>
+      <c r="I84">
         <v>0.2</v>
       </c>
-      <c r="M81" t="s">
+      <c r="M84" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A82" t="s">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
         <v>105</v>
       </c>
-      <c r="B82">
+      <c r="B85">
         <v>1991</v>
       </c>
-      <c r="C82">
+      <c r="C85">
         <f>7.5/12</f>
         <v>0.625</v>
       </c>
-      <c r="D82">
-        <f>SUM(B82:C82)</f>
+      <c r="D85">
+        <f>SUM(B85:C85)</f>
         <v>1991.625</v>
       </c>
-      <c r="E82" t="s">
+      <c r="E85" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A83" t="s">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
         <v>108</v>
       </c>
-      <c r="B83">
+      <c r="B86">
         <v>1993</v>
       </c>
-      <c r="C83">
+      <c r="C86">
         <f>10.5/12</f>
         <v>0.875</v>
       </c>
-      <c r="D83">
-        <f t="shared" ref="D83" si="12">SUM(B83:C83)</f>
+      <c r="D86">
+        <f t="shared" ref="D86" si="12">SUM(B86:C86)</f>
         <v>1993.875</v>
       </c>
-      <c r="E83" t="s">
+      <c r="E86" t="s">
         <v>109</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M62" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:M65" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <hyperlinks>
-    <hyperlink ref="M45" r:id="rId1" xr:uid="{2C6F6E23-ECE2-48FD-9281-2D99D7593433}"/>
-    <hyperlink ref="M78" r:id="rId2" location="Sec2234" xr:uid="{62C0EF63-5AB8-4BA9-8B91-BED051CAB1BF}"/>
-    <hyperlink ref="M79" r:id="rId3" xr:uid="{B20578A3-8323-4DE4-85AE-68D7FF9E102B}"/>
+    <hyperlink ref="M47" r:id="rId1" xr:uid="{2C6F6E23-ECE2-48FD-9281-2D99D7593433}"/>
+    <hyperlink ref="M81" r:id="rId2" location="Sec2234" xr:uid="{62C0EF63-5AB8-4BA9-8B91-BED051CAB1BF}"/>
+    <hyperlink ref="M82" r:id="rId3" xr:uid="{B20578A3-8323-4DE4-85AE-68D7FF9E102B}"/>
     <hyperlink ref="M2" r:id="rId4" location="Sec2" xr:uid="{E3E93F9E-DE58-4D08-B99F-BCC6036F7008}"/>
     <hyperlink ref="M3" r:id="rId5" xr:uid="{D9A4AF65-DA70-469D-830F-18C855356D90}"/>
     <hyperlink ref="M4" r:id="rId6" xr:uid="{B12BC68D-68E4-4106-B5E4-E526B322A8A6}"/>
@@ -3513,23 +3617,23 @@
     <hyperlink ref="M11" r:id="rId28" xr:uid="{F4B38A8C-4738-4863-988E-62EDE0DDB3C8}"/>
     <hyperlink ref="M8" r:id="rId29" xr:uid="{EB34F27E-0B05-4195-B7F0-D388A7AD2D27}"/>
     <hyperlink ref="M6" r:id="rId30" xr:uid="{15DB38CB-6521-44E4-B260-EDC4586943ED}"/>
-    <hyperlink ref="M48" r:id="rId31" location="Sec2" xr:uid="{235DA6CA-59BB-493F-AE3F-01F1CACCC335}"/>
-    <hyperlink ref="M50" r:id="rId32" location="BIB8" xr:uid="{93BE3110-5F69-4CA6-9551-CCF063F7F511}"/>
-    <hyperlink ref="M53" r:id="rId33" xr:uid="{1DFC047B-89FD-4940-B346-4D1719C84B8D}"/>
-    <hyperlink ref="M54" r:id="rId34" location="Sec11" xr:uid="{CF173C6B-1889-4F7C-B611-E21261B20B04}"/>
+    <hyperlink ref="M50" r:id="rId31" location="Sec2" xr:uid="{235DA6CA-59BB-493F-AE3F-01F1CACCC335}"/>
+    <hyperlink ref="M52" r:id="rId32" location="BIB8" xr:uid="{93BE3110-5F69-4CA6-9551-CCF063F7F511}"/>
+    <hyperlink ref="M55" r:id="rId33" xr:uid="{1DFC047B-89FD-4940-B346-4D1719C84B8D}"/>
+    <hyperlink ref="M56" r:id="rId34" location="Sec11" xr:uid="{CF173C6B-1889-4F7C-B611-E21261B20B04}"/>
     <hyperlink ref="M34" r:id="rId35" xr:uid="{1D1CA4DD-57EB-4FDA-B205-CD4F57860135}"/>
-    <hyperlink ref="M55" r:id="rId36" xr:uid="{5E0A0525-EF60-4BC3-816C-A0AF61B86230}"/>
-    <hyperlink ref="M56" r:id="rId37" xr:uid="{FBA91335-F556-49C3-8074-1B1FB90338FD}"/>
-    <hyperlink ref="M58" r:id="rId38" xr:uid="{1BA0974D-F2A5-4829-A486-BF96B8249301}"/>
-    <hyperlink ref="M76" r:id="rId39" xr:uid="{5A113D17-20D4-4ECC-A635-501B5C41F205}"/>
-    <hyperlink ref="M60" r:id="rId40" xr:uid="{FF006124-F785-4CEA-AFB9-38325E6F1CED}"/>
-    <hyperlink ref="M61" r:id="rId41" xr:uid="{64B6CE76-216E-455F-B948-EF8356A331AA}"/>
-    <hyperlink ref="M47" r:id="rId42" xr:uid="{497E408F-53E2-49B7-8F16-9DD7EA2ED202}"/>
-    <hyperlink ref="M41" r:id="rId43" location="sec2" xr:uid="{5034959D-6751-4851-84E0-172E272F75EE}"/>
-    <hyperlink ref="M43" r:id="rId44" xr:uid="{B7EB3734-AC4C-4151-A101-96D04051FDCD}"/>
-    <hyperlink ref="M44" r:id="rId45" xr:uid="{C91CD542-20C8-4FDA-BF4B-40DD95619963}"/>
-    <hyperlink ref="M40" r:id="rId46" location=":~:text=To%20comply%20with%20this%20purpose,protein%20production%20in%20microbial%20fermentations." xr:uid="{1A9C7341-CCC1-4312-91A0-12EA871608D9}"/>
-    <hyperlink ref="M42" r:id="rId47" xr:uid="{AA476111-326A-4868-8FB2-D9580E4ACE47}"/>
+    <hyperlink ref="M58" r:id="rId36" xr:uid="{5E0A0525-EF60-4BC3-816C-A0AF61B86230}"/>
+    <hyperlink ref="M59" r:id="rId37" xr:uid="{FBA91335-F556-49C3-8074-1B1FB90338FD}"/>
+    <hyperlink ref="M61" r:id="rId38" xr:uid="{1BA0974D-F2A5-4829-A486-BF96B8249301}"/>
+    <hyperlink ref="M79" r:id="rId39" xr:uid="{5A113D17-20D4-4ECC-A635-501B5C41F205}"/>
+    <hyperlink ref="M63" r:id="rId40" xr:uid="{FF006124-F785-4CEA-AFB9-38325E6F1CED}"/>
+    <hyperlink ref="M64" r:id="rId41" xr:uid="{64B6CE76-216E-455F-B948-EF8356A331AA}"/>
+    <hyperlink ref="M49" r:id="rId42" xr:uid="{497E408F-53E2-49B7-8F16-9DD7EA2ED202}"/>
+    <hyperlink ref="M43" r:id="rId43" location="sec2" xr:uid="{5034959D-6751-4851-84E0-172E272F75EE}"/>
+    <hyperlink ref="M45" r:id="rId44" xr:uid="{B7EB3734-AC4C-4151-A101-96D04051FDCD}"/>
+    <hyperlink ref="M46" r:id="rId45" xr:uid="{C91CD542-20C8-4FDA-BF4B-40DD95619963}"/>
+    <hyperlink ref="M42" r:id="rId46" location=":~:text=To%20comply%20with%20this%20purpose,protein%20production%20in%20microbial%20fermentations." xr:uid="{1A9C7341-CCC1-4312-91A0-12EA871608D9}"/>
+    <hyperlink ref="M44" r:id="rId47" xr:uid="{AA476111-326A-4868-8FB2-D9580E4ACE47}"/>
     <hyperlink ref="M35" r:id="rId48" xr:uid="{A35E98C5-C6A9-4A33-A079-EEED0DDD2B60}"/>
     <hyperlink ref="M36" r:id="rId49" location="fig0020" xr:uid="{0D4AA659-B49F-4D5C-9A30-E24621D94128}"/>
     <hyperlink ref="M37" r:id="rId50" location="Sec18" xr:uid="{FFBE9CB1-C680-4B2B-81BA-60FEBB39DFC0}"/>
